--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -112,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -177,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1004,7 +861,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1288,7 +1145,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1664,7 +1521,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1902,7 +1759,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2704,7 +2561,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2750,7 +2607,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-26</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3272,7 +3129,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3318,7 +3175,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3556,7 +3413,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-30</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3602,7 +3459,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3836,7 +3693,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-11</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3882,7 +3739,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4120,7 +3977,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4166,7 +4023,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4404,7 +4261,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4450,7 +4307,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4688,7 +4545,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-08</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4734,7 +4591,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4780,7 +4637,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4972,7 +4829,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5018,7 +4875,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5064,7 +4921,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2022-02-15</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5110,7 +4967,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-25</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5252,7 +5109,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5298,7 +5155,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5344,7 +5201,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5390,7 +5247,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5536,7 +5393,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5582,7 +5439,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5628,7 +5485,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5674,7 +5531,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5866,7 +5723,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5912,7 +5769,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -6104,7 +5961,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6150,7 +6007,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6196,7 +6053,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6242,7 +6099,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-16</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6388,7 +6245,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-18</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6434,7 +6291,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6480,7 +6337,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6526,7 +6383,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6672,7 +6529,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6718,7 +6575,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6810,7 +6667,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6956,7 +6813,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -7002,7 +6859,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -7048,7 +6905,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7094,7 +6951,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7240,7 +7097,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-19</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7286,7 +7143,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7332,7 +7189,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7378,7 +7235,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7616,7 +7473,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7662,7 +7519,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7808,7 +7665,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-31</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7900,7 +7757,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7946,7 +7803,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -8092,7 +7949,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -8138,7 +7995,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8184,7 +8041,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8230,7 +8087,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-04</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8376,7 +8233,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-13</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8422,7 +8279,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8468,7 +8325,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-16</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8514,7 +8371,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-29</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8660,7 +8517,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8706,7 +8563,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8752,7 +8609,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-23</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8798,7 +8655,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8944,7 +8801,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8990,7 +8847,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -9082,7 +8939,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -9228,7 +9085,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-15</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9274,7 +9131,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9366,7 +9223,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-07</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9512,7 +9369,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-14</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9650,7 +9507,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9796,7 +9653,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9934,7 +9791,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -10080,7 +9937,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -10218,7 +10075,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-28</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10548,7 +10405,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10686,7 +10543,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10916,7 +10773,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10962,7 +10819,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -11054,7 +10911,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -11238,7 +11095,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11330,7 +11187,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-25</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11514,7 +11371,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11606,7 +11463,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2022-06-12</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11744,7 +11601,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11790,7 +11647,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-03</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11882,7 +11739,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-11</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -11928,7 +11785,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -12066,7 +11923,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -12204,7 +12061,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-06-05</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12342,7 +12199,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12388,7 +12245,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12434,7 +12291,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12480,7 +12337,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12618,7 +12475,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12664,7 +12521,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-17</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12756,7 +12613,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -12802,7 +12659,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-17</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12894,7 +12751,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -12940,7 +12797,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -13032,7 +12889,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-11</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -13170,7 +13027,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-02</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -13216,7 +13073,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -13308,7 +13165,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-27</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13354,7 +13211,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13400,7 +13257,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13446,7 +13303,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13492,7 +13349,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13676,7 +13533,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13722,7 +13579,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13768,7 +13625,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13860,7 +13717,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13952,7 +13809,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13998,7 +13855,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -14044,7 +13901,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -14090,7 +13947,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -14136,7 +13993,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -14182,7 +14039,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14274,7 +14131,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14320,7 +14177,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14412,7 +14269,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14458,7 +14315,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14504,7 +14361,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14550,7 +14407,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14596,7 +14453,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-31</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14688,7 +14545,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14734,7 +14591,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14780,7 +14637,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14826,7 +14683,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14964,7 +14821,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -15010,7 +14867,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -15056,7 +14913,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -15102,7 +14959,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -15148,7 +15005,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -15240,7 +15097,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15286,7 +15143,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15332,7 +15189,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15378,7 +15235,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -15516,7 +15373,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -15562,7 +15419,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -15608,7 +15465,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -15654,7 +15511,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -15838,7 +15695,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -15884,7 +15741,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -15930,7 +15787,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -16068,7 +15925,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -16160,7 +16017,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16206,7 +16063,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16344,7 +16201,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -16390,7 +16247,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16482,7 +16339,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -16620,7 +16477,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -16666,7 +16523,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -16712,7 +16569,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -16758,7 +16615,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -16896,7 +16753,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-28</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -16988,7 +16845,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -17034,7 +16891,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -17172,7 +17029,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-29</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -17218,7 +17075,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -17264,7 +17121,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17310,7 +17167,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17448,7 +17305,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17494,7 +17351,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17540,7 +17397,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -17586,7 +17443,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -17724,7 +17581,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -17770,7 +17627,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-25</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -17816,7 +17673,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-05</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -17862,7 +17719,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -18000,7 +17857,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-10</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -18046,7 +17903,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-06</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -18092,7 +17949,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -18138,7 +17995,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -18276,7 +18133,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-23</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -18322,7 +18179,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -18368,7 +18225,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18414,7 +18271,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18552,7 +18409,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18598,7 +18455,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -18644,7 +18501,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -18690,7 +18547,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -18828,7 +18685,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-08</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -18874,7 +18731,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -18920,7 +18777,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -19104,7 +18961,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -19150,7 +19007,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-27</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -19196,7 +19053,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-27</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -19242,7 +19099,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -19380,7 +19237,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -19426,7 +19283,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -19472,7 +19329,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19540,3986 +19397,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley III - 3A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>202 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>136 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>50 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$567万
-$23,804/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$545万
-$23,782/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$908万
-$24,748/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$783万
-$21,995/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$563万
-$23,672/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$670万
-$29,242/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$898万
-$24,467/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$774万
-$21,747/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$524万
-$22,000/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$683万
-$29,819/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$832万
-$22,674/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$983万
-$27,619/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$527万
-$22,125/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$515万
-$22,501/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$830万
-$22,609/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$848万
-$23,831/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$683万
-$28,708/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$691万
-$30,162/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$905万
-$24,670/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$846万
-$23,763/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$518万
-$21,753/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$512万
-$22,368/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2,592万
-$33,443/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$903万
-$24,601/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$844万
-$23,695/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$522万
-$21,939/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$511万
-$22,303/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$883万
-$24,048/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$825万
-$23,162/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$678万
-$28,468/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$650万
-$28,404/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$880万
-$23,977/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$822万
-$23,094/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$513万
-$21,570/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$508万
-$22,173/呎
-(25年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$818万
-$22,283/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$820万
-$23,029/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$674万
-$28,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$667万
-$29,126/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2,522万
-$32,542/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$815万
-$22,216/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$834万
-$23,418/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$686万
-$28,827/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$645万
-$28,152/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$813万
-$22,151/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$831万
-$23,350/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$684万
-$28,745/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$650万
-$28,364/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$808万
-$22,020/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$826万
-$23,212/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$659万
-$27,705/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$659万
-$28,783/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$838万
-$22,832/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$824万
-$23,144/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$664万
-$27,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$657万
-$28,694/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$803万
-$21,889/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$979万
-$27,509/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$676万
-$28,416/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$642万
-$28,024/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 775呎 (3房)
-$2,483万
-$32,041/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,077万
-$29,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$956万
-$26,866/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$674万
-$28,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$653万
-$28,523/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,041万
-$28,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$944万
-$26,506/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$672万
-$28,251/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$631万
-$27,566/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,060万
-$28,877/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$951万
-$26,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$650万
-$27,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$649万
-$28,352/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$794万
-$21,627/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$958万
-$26,904/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$668万
-$28,086/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$654万
-$28,550/呎
-(21年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,011万
-$27,542/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$965万
-$27,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$646万
-$27,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$645万
-$28,176/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,021万
-$27,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$965万
-$27,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$660万
-$27,718/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$645万
-$28,176/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,040万
-$28,326/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$962万
-$27,016/呎
-(21年-10月)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$644万
-$27,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$624万
-$27,231/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,047万
-$28,529/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$949万
-$26,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$663万
-$27,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$641万
-$28,005/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,012万
-$27,581/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$956万
-$26,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$661万
-$27,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$639万
-$27,919/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$999万
-$27,208/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$943万
-$26,498/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$665万
-$27,957/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$644万
-$28,113/呎
-(21年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,004万
-$27,356/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$918万
-$25,791/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$641万
-$26,948/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$635万
-$27,748/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$980万
-$26,709/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$915万
-$25,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$633万
-$26,588/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$612万
-$26,728/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$26,990/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$915万
-$25,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$639万
-$26,868/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$631万
-$27,572/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$998万
-$27,186/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$922万
-$25,901/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$631万
-$26,508/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$629万
-$27,487/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$984万
-$26,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$767万
-$21,545/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$625万
-$26,268/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$611万
-$26,670/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$27,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$760万
-$21,342/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$633万
-$26,577/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$599万
-$26,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$965万
-$26,292/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$757万
-$21,276/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$569万
-$23,900/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$597万
-$26,056/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>A | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$969万
-$26,401/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$753万
-$21,140/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$466万
-$19,595/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$599万
-$26,163/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="20" t="inlineStr"/>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>C | 374呎 (1房)
-$971万
-$25,957/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$745万
-$20,937/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$462万
-$19,415/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$587万
-$25,654/呎
-(24年-03月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The Henley III - 3B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>202 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>29 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>160 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,321万
-$36,000/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$1,216万
-$34,166/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$561万
-$23,563/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$682万
-$29,782/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,572万
-$33,107/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,936万
-$35,852/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,073万
-$29,227/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$776万
-$21,801/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$558万
-$23,435/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$644万
-$28,131/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,543万
-$32,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,914万
-$35,446/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,039万
-$28,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$990万
-$27,818/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$518万
-$21,772/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$499万
-$21,772/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,582万
-$33,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,903万
-$35,244/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,055万
-$28,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$763万
-$21,428/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$515万
-$21,650/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$496万
-$21,642/呎
-(25年-07月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,521万
-$32,450/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,803万
-$33,385/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,030万
-$28,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$761万
-$21,366/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$514万
-$21,588/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$581万
-$25,386/呎
-(24年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,541万
-$32,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,892万
-$35,041/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,027万
-$27,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$979万
-$27,497/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$512万
-$21,529/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$580万
-$25,314/呎
-(24年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,507万
-$32,263/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,887万
-$34,939/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,024万
-$27,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$756万
-$21,241/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$511万
-$21,467/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$654万
-$28,554/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,526万
-$32,466/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,806万
-$33,445/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,021万
-$27,827/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$754万
-$21,177/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$509万
-$21,404/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$626万
-$27,322/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,532万
-$32,581/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,782万
-$33,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,029万
-$28,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$752万
-$21,115/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$508万
-$21,364/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$630万
-$27,525/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,485万
-$31,981/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,814万
-$33,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,015万
-$27,666/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$750万
-$21,054/呎
-(25年-07月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$660万
-$27,729/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$629万
-$27,446/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,478万
-$31,888/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,791万
-$33,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,055万
-$28,748/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$747万
-$20,992/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$509万
-$21,371/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$620万
-$27,077/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,470万
-$31,794/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,767万
-$32,725/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$1,020万
-$27,795/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$982万
-$27,578/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$663万
-$27,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$618万
-$26,998/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,585万
-$33,228/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,757万
-$32,531/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$994万
-$27,076/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$937万
-$26,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$496万
-$20,827/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$634万
-$27,684/呎
-(21年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,449万
-$31,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,733万
-$32,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$26,996/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$944万
-$26,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$494万
-$20,768/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$619万
-$27,035/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,570万
-$33,030/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,728万
-$32,003/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$988万
-$26,918/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$960万
-$26,980/呎
-(21年-11月)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$655万
-$27,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$617万
-$26,955/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,562万
-$32,931/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,740万
-$32,230/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$985万
-$26,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$958万
-$26,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$653万
-$27,457/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$615万
-$26,872/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,554万
-$32,833/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,826万
-$33,824/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$982万
-$26,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$925万
-$25,997/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$665万
-$27,946/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$620万
-$27,071/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,547万
-$32,734/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,748万
-$32,375/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$989万
-$26,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$932万
-$26,192/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$656万
-$27,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$612万
-$26,708/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,539万
-$32,635/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,816万
-$33,622/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$987万
-$26,883/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$920万
-$25,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$654万
-$27,498/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$610万
-$26,628/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,405万
-$30,949/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,720万
-$31,844/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$973万
-$26,522/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$936万
-$26,304/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$659万
-$27,699/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$602万
-$26,268/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,531万
-$32,536/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,810万
-$33,520/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$984万
-$26,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$936万
-$26,304/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$639万
-$26,851/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$602万
-$26,268/呎
-(21年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,398万
-$30,856/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,805万
-$33,419/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$981万
-$26,723/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$943万
-$26,493/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$657万
-$27,617/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$600万
-$26,189/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,516万
-$32,339/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,799万
-$33,319/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$998万
-$27,197/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$940万
-$26,413/呎
-(21年-09月)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$649万
-$27,253/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$598万
-$26,106/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,508万
-$32,240/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,794万
-$33,217/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$995万
-$27,117/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$937万
-$26,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F29" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$653万
-$27,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G29" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$609万
-$26,575/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>A | 777呎 (3房)
-$2,376万
-$30,575/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,788万
-$33,115/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$972万
-$26,482/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$906万
-$25,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F30" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$480万
-$20,162/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="G30" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$613万
-$26,764/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,462万
-$31,649/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,761万
-$32,607/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$957万
-$26,085/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$909万
-$25,540/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F31" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$634万
-$26,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G31" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$597万
-$26,054/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,455万
-$31,550/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,755万
-$32,507/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$974万
-$26,545/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$898万
-$25,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$632万
-$26,553/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$589万
-$25,704/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,455万
-$31,550/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,755万
-$32,507/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$954万
-$26,004/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$898万
-$25,218/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F33" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$625万
-$26,276/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G33" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$595万
-$25,974/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,447万
-$31,451/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,750万
-$32,406/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$991万
-$27,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E34" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$904万
-$25,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$631万
-$26,505/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$593万
-$25,890/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B35" s="21" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,439万
-$31,353/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,744万
-$32,304/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$988万
-$26,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$914万
-$25,681/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F35" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$622万
-$26,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$581万
-$25,380/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,432万
-$31,254/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,739万
-$32,202/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$975万
-$26,564/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$896万
-$25,179/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$627万
-$26,327/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$582万
-$25,400/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="65" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,416万
-$31,057/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C37" s="21" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,728万
-$32,000/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$738万
-$20,096/呎
-(25年-06月)</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$875万
-$24,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$625万
-$26,247/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$592万
-$25,848/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="65" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>A | 778呎 (3房)
-$2,393万
-$30,762/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>B | 540呎 (2房)
-$1,712万
-$31,696/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>C | 367呎 (1房)
-$936万
-$25,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$870万
-$24,425/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$621万
-$26,085/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G38" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$577万
-$25,186/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="65" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr"/>
-      <c r="C39" s="20" t="inlineStr"/>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>C | 374呎 (1房)
-$739万
-$19,765/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-$861万
-$24,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F39" s="18" t="inlineStr">
-        <is>
-          <t>E | 238呎 (开放式)
-$609万
-$25,574/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>F | 229呎 (开放式)
-$576万
-$25,139/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +43,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +154,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +235,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -19397,4 +19594,3986 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$567万
+$23,804/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$545万
+$23,782/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$908万
+$24,748/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$783万
+$21,995/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$563万
+$23,672/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$670万
+$29,242/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$898万
+$24,467/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$774万
+$21,747/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$524万
+$22,000/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$683万
+$29,819/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$832万
+$22,674/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$983万
+$27,619/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$527万
+$22,125/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$515万
+$22,501/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$830万
+$22,609/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$848万
+$23,831/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$683万
+$28,708/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$691万
+$30,162/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$905万
+$24,670/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$846万
+$23,763/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$518万
+$21,753/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$512万
+$22,368/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2592万
+$33,443/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$903万
+$24,601/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$844万
+$23,695/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$522万
+$21,939/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$511万
+$22,303/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$883万
+$24,048/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$825万
+$23,162/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$678万
+$28,468/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$650万
+$28,404/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$880万
+$23,977/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$822万
+$23,094/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$513万
+$21,570/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$508万
+$22,173/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$818万
+$22,283/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$820万
+$23,029/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$674万
+$28,320/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$667万
+$29,126/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2522万
+$32,542/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$815万
+$22,216/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$834万
+$23,418/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$686万
+$28,827/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$645万
+$28,152/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$813万
+$22,151/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$831万
+$23,350/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$684万
+$28,745/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$650万
+$28,364/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$808万
+$22,020/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$826万
+$23,212/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$659万
+$27,705/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$659万
+$28,783/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$838万
+$22,832/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$824万
+$23,144/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$664万
+$27,916/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$657万
+$28,694/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$803万
+$21,889/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$979万
+$27,509/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$676万
+$28,416/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$642万
+$28,024/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 775呎 (3房)
+$2483万
+$32,041/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1077万
+$29,343/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$956万
+$26,866/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$674万
+$28,333/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$653万
+$28,523/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1041万
+$28,378/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$944万
+$26,506/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$672万
+$28,251/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$631万
+$27,566/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1060万
+$28,877/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$951万
+$26,704/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$650万
+$27,306/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$649万
+$28,352/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$794万
+$21,627/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$958万
+$26,904/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$668万
+$28,086/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$654万
+$28,550/呎
+(21年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1011万
+$27,542/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$965万
+$27,099/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$646万
+$27,147/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$645万
+$28,176/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1021万
+$27,832/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$965万
+$27,099/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$660万
+$27,718/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$645万
+$28,176/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1040万
+$28,326/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$962万
+$27,016/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$644万
+$27,067/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$624万
+$27,231/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1047万
+$28,529/呎
+(22年-10月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$949万
+$26,658/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$663万
+$27,839/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$641万
+$28,005/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1012万
+$27,581/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$956万
+$26,851/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$661万
+$27,757/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$639万
+$27,919/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$999万
+$27,208/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$943万
+$26,498/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$665万
+$27,957/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$644万
+$28,113/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1004万
+$27,356/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$918万
+$25,791/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$641万
+$26,948/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$635万
+$27,748/呎
+(21年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$980万
+$26,709/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$915万
+$25,711/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$633万
+$26,588/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$612万
+$26,728/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$991万
+$26,990/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$915万
+$25,711/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$639万
+$26,868/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$631万
+$27,572/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$998万
+$27,186/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$922万
+$25,901/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$631万
+$26,508/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$629万
+$27,487/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$984万
+$26,822/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$767万
+$21,545/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$625万
+$26,268/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$611万
+$26,670/呎
+(22年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$991万
+$27,014/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$760万
+$21,342/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$633万
+$26,577/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$599万
+$26,139/呎
+(21年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$965万
+$26,292/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$757万
+$21,276/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$569万
+$23,900/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$597万
+$26,056/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>A | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$969万
+$26,401/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$753万
+$21,140/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$466万
+$19,595/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$599万
+$26,163/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr"/>
+      <c r="C38" s="24" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 374呎 (1房)
+$971万
+$25,957/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$745万
+$20,937/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$462万
+$19,415/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$587万
+$25,654/呎
+(22年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1321万
+$36,000/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$1216万
+$34,166/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$561万
+$23,563/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$682万
+$29,782/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2572万
+$33,107/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1936万
+$35,852/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1073万
+$29,227/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$776万
+$21,801/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$558万
+$23,435/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$644万
+$28,131/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2543万
+$32,689/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1914万
+$35,446/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1039万
+$28,306/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$990万
+$27,818/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$518万
+$21,772/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$499万
+$21,772/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2582万
+$33,230/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1903万
+$35,244/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1055万
+$28,738/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$763万
+$21,428/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$515万
+$21,650/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$496万
+$21,642/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2521万
+$32,450/呎
+(22年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1803万
+$33,385/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1030万
+$28,065/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$761万
+$21,366/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$514万
+$21,588/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$581万
+$25,386/呎
+(24年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2541万
+$32,655/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1892万
+$35,041/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1027万
+$27,985/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$979万
+$27,497/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$512万
+$21,529/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$580万
+$25,314/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2507万
+$32,263/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1887万
+$34,939/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1024万
+$27,905/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$756万
+$21,241/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$511万
+$21,467/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$654万
+$28,554/呎
+(22年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2526万
+$32,466/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1806万
+$33,445/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1021万
+$27,827/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$754万
+$21,177/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$509万
+$21,404/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$626万
+$27,322/呎
+(22年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2532万
+$32,581/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1782万
+$33,000/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1029万
+$28,039/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$752万
+$21,115/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$508万
+$21,364/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$630万
+$27,525/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2485万
+$31,981/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1814万
+$33,596/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1015万
+$27,666/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$750万
+$21,054/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$660万
+$27,729/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$629万
+$27,446/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2478万
+$31,888/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1791万
+$33,163/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1055万
+$28,748/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$747万
+$20,992/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$509万
+$21,371/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$620万
+$27,077/呎
+(22年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2470万
+$31,794/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1767万
+$32,725/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$1020万
+$27,795/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$982万
+$27,578/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$663万
+$27,860/呎
+(22年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$618万
+$26,998/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2585万
+$33,228/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1757万
+$32,531/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$994万
+$27,076/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$937万
+$26,312/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$496万
+$20,827/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$634万
+$27,684/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2449万
+$31,513/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1733万
+$32,098/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$991万
+$26,996/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$944万
+$26,510/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$494万
+$20,768/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$619万
+$27,035/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2570万
+$33,030/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1728万
+$32,003/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$988万
+$26,918/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$960万
+$26,980/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$655万
+$27,537/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$617万
+$26,955/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2562万
+$32,931/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1740万
+$32,230/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$985万
+$26,838/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$958万
+$26,900/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$653万
+$27,457/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$615万
+$26,872/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2554万
+$32,833/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1826万
+$33,824/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$982万
+$26,760/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$925万
+$25,997/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$665万
+$27,946/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$620万
+$27,071/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2547万
+$32,734/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1748万
+$32,375/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$989万
+$26,961/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$932万
+$26,192/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$656万
+$27,579/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$612万
+$26,708/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2539万
+$32,635/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1816万
+$33,622/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$987万
+$26,883/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$920万
+$25,839/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$654万
+$27,498/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$610万
+$26,628/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2405万
+$30,949/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1720万
+$31,844/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$973万
+$26,522/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$936万
+$26,304/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$659万
+$27,699/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$602万
+$26,268/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2531万
+$32,536/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1810万
+$33,520/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$984万
+$26,801/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$936万
+$26,304/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$639万
+$26,851/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$602万
+$26,268/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2398万
+$30,856/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1805万
+$33,419/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$981万
+$26,723/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$943万
+$26,493/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$657万
+$27,617/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$600万
+$26,189/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2516万
+$32,339/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1799万
+$33,319/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$998万
+$27,197/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$940万
+$26,413/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$649万
+$27,253/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$598万
+$26,106/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2508万
+$32,240/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1794万
+$33,217/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$995万
+$27,117/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$937万
+$26,331/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$653万
+$27,452/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$609万
+$26,575/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>A | 777呎 (3房)
+$2376万
+$30,575/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1788万
+$33,115/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$972万
+$26,482/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$906万
+$25,447/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$480万
+$20,162/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$613万
+$26,764/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2462万
+$31,649/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1761万
+$32,607/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$957万
+$26,085/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$909万
+$25,540/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$634万
+$26,650/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$597万
+$26,054/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2455万
+$31,550/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1755万
+$32,507/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$974万
+$26,545/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$898万
+$25,226/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$632万
+$26,553/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$589万
+$25,704/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2455万
+$31,550/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1755万
+$32,507/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$954万
+$26,004/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$898万
+$25,218/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$625万
+$26,276/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$595万
+$25,974/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2447万
+$31,451/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1750万
+$32,406/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$991万
+$27,002/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$904万
+$25,397/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$631万
+$26,505/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$593万
+$25,890/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2439万
+$31,353/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1744万
+$32,304/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$988万
+$26,919/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$914万
+$25,681/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$622万
+$26,133/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$581万
+$25,380/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2432万
+$31,254/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1739万
+$32,202/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$975万
+$26,564/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$896万
+$25,179/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$627万
+$26,327/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$582万
+$25,400/呎
+(22年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2416万
+$31,057/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1728万
+$32,000/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$738万
+$20,096/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$875万
+$24,583/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$625万
+$26,247/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$592万
+$25,848/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>A | 778呎 (3房)
+$2393万
+$30,762/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>B | 540呎 (2房)
+$1712万
+$31,696/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>C | 367呎 (1房)
+$936万
+$25,510/呎
+(21年-09月)</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$870万
+$24,425/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$621万
+$26,085/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$577万
+$25,186/呎
+(22年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr"/>
+      <c r="C38" s="24" t="inlineStr"/>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>C | 374呎 (1房)
+$739万
+$19,765/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+$861万
+$24,188/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>E | 238呎 (开放式)
+$609万
+$25,574/呎
+(22年-08月)</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="inlineStr">
+        <is>
+          <t>F | 229呎 (开放式)
+$576万
+$25,139/呎
+(22年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -671,7 +671,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -2369,14 +2369,14 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>5663740</v>
+        <v>6285370</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>24732</v>
+        <v>27447</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -13845,14 +13845,14 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>5592400</v>
+        <v>6206200</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>24421</v>
+        <v>27101</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13969,14 +13969,14 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>9973660</v>
+        <v>11068330</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>28016</v>
+        <v>31091</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -14031,14 +14031,14 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>10833840</v>
+        <v>12022920</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>29520</v>
+        <v>32760</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
@@ -14481,14 +14481,14 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>15875200</v>
+        <v>18682400</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>29399</v>
+        <v>34597</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
@@ -14853,14 +14853,14 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>15695620</v>
+        <v>18471065</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>29066</v>
+        <v>34206</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
@@ -15225,14 +15225,14 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>15606240</v>
+        <v>18365880</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>28900</v>
+        <v>34011</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
@@ -15969,14 +15969,14 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>15516040</v>
+        <v>18259730</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>28733</v>
+        <v>33814</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -16341,14 +16341,14 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>15470940</v>
+        <v>18206655</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>28650</v>
+        <v>33716</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
@@ -18635,14 +18635,14 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>21197820</v>
+        <v>24946215</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>27247</v>
+        <v>32065</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -19379,14 +19379,14 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>21071540</v>
+        <v>24797605</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>27084</v>
+        <v>31874</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -20061,14 +20061,14 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>14977300</v>
+        <v>17625725</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>27736</v>
+        <v>32640</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
@@ -21921,14 +21921,14 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>14797720</v>
+        <v>17414390</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>27403</v>
+        <v>32249</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
@@ -22293,14 +22293,14 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>14753440</v>
+        <v>17362280</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>27321</v>
+        <v>32152</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
@@ -22355,14 +22355,14 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>20631200</v>
+        <v>24279400</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>26518</v>
+        <v>31207</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
@@ -22727,14 +22727,14 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>20568060</v>
+        <v>24205095</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>26437</v>
+        <v>31112</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
@@ -23409,14 +23409,14 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>14438560</v>
+        <v>16991720</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>26738</v>
+        <v>31466</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
@@ -23471,14 +23471,14 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>20190860</v>
+        <v>23761195</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>25952</v>
+        <v>30541</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
@@ -23781,14 +23781,14 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>14394280</v>
+        <v>16939610</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>26656</v>
+        <v>31370</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
@@ -23843,14 +23843,14 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>20127720</v>
+        <v>23686890</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>25871</v>
+        <v>30446</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -24153,14 +24153,14 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>14394280</v>
+        <v>16939610</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>26656</v>
+        <v>31370</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
@@ -24215,14 +24215,14 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>20127720</v>
+        <v>23686890</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>25871</v>
+        <v>30446</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
@@ -24525,14 +24525,14 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>14349180</v>
+        <v>16886535</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>26573</v>
+        <v>31271</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
@@ -24587,14 +24587,14 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>20064580</v>
+        <v>23612585</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>25790</v>
+        <v>30350</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24897,14 +24897,14 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>14304080</v>
+        <v>16833460</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>26489</v>
+        <v>31173</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
@@ -24959,14 +24959,14 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>20002260</v>
+        <v>23539245</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>25710</v>
+        <v>30256</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
@@ -25269,14 +25269,14 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>14258980</v>
+        <v>16780385</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>26406</v>
+        <v>31075</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
@@ -25331,14 +25331,14 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>19939120</v>
+        <v>23464940</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>25629</v>
+        <v>30161</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
@@ -25641,14 +25641,14 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>14169600</v>
+        <v>16675200</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>26240</v>
+        <v>30880</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -25703,14 +25703,14 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>19812840</v>
+        <v>23316330</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>25466</v>
+        <v>29970</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
@@ -26013,14 +26013,14 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>14035120</v>
+        <v>16516940</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>25991</v>
+        <v>30587</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
@@ -26075,14 +26075,14 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>19625060</v>
+        <v>23095345</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>25225</v>
+        <v>29686</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -676,7 +676,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2369,18 +2369,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6285370</v>
+        <v>6253800</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>27447</v>
+        <v>27309</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -13845,18 +13845,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>6206200</v>
+        <v>6175100</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>27101</v>
+        <v>26966</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13969,18 +13969,18 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>11068330</v>
+        <v>11012900</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>31091</v>
+        <v>30935</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14031,18 +14031,18 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.46%</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>12022920</v>
+        <v>11962700</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>32760</v>
+        <v>32596</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14481,18 +14481,18 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>18682400</v>
+        <v>17888300</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>34597</v>
+        <v>33126</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14853,18 +14853,18 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>18471065</v>
+        <v>17685900</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>34206</v>
+        <v>32752</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15225,18 +15225,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>18365880</v>
+        <v>17585200</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>34011</v>
+        <v>32565</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15969,18 +15969,18 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>18259730</v>
+        <v>17483600</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>33814</v>
+        <v>32377</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16341,18 +16341,18 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>18206655</v>
+        <v>17432800</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>33716</v>
+        <v>32283</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -18635,18 +18635,18 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>24946215</v>
+        <v>23761200</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>32065</v>
+        <v>30541</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -19379,18 +19379,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>24797605</v>
+        <v>23619700</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>31874</v>
+        <v>30360</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -19751,18 +19751,18 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>21008400</v>
+        <v>23548900</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>27003</v>
+        <v>30269</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -20061,18 +20061,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>17625725</v>
+        <v>16876600</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>32640</v>
+        <v>31253</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -20123,18 +20123,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>20946080</v>
+        <v>23479000</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>26923</v>
+        <v>30179</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20495,18 +20495,18 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>20882940</v>
+        <v>23408200</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>26842</v>
+        <v>30088</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -20805,18 +20805,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>14887920</v>
+        <v>16775800</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>27570</v>
+        <v>31066</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20867,18 +20867,18 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>20819800</v>
+        <v>23337400</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>26761</v>
+        <v>29997</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N318" s="3" t="inlineStr">
@@ -21549,18 +21549,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>14842820</v>
+        <v>16725000</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>27487</v>
+        <v>30972</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -21611,18 +21611,18 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>20756660</v>
+        <v>23266700</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>26680</v>
+        <v>29906</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -21921,18 +21921,18 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>17414390</v>
+        <v>16674100</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>32249</v>
+        <v>30878</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22293,18 +22293,18 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>17362280</v>
+        <v>16624300</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>32152</v>
+        <v>30786</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr">
@@ -22355,18 +22355,18 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>24279400</v>
+        <v>23126100</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>31207</v>
+        <v>29725</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22665,18 +22665,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>14708340</v>
+        <v>16573500</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>27238</v>
+        <v>30692</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -22727,18 +22727,18 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>24205095</v>
+        <v>23055200</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>31112</v>
+        <v>29634</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23037,18 +23037,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>14663240</v>
+        <v>16522700</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>27154</v>
+        <v>30598</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -23409,18 +23409,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>16991720</v>
+        <v>16269500</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>31466</v>
+        <v>30129</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23471,18 +23471,18 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>23761195</v>
+        <v>22632400</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>30541</v>
+        <v>29090</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -23781,18 +23781,18 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>16939610</v>
+        <v>16219600</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>31370</v>
+        <v>30036</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N365" s="3" t="inlineStr">
@@ -23843,18 +23843,18 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>23686890</v>
+        <v>22561600</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>30446</v>
+        <v>28999</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -24153,18 +24153,18 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>16939610</v>
+        <v>16219600</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>31370</v>
+        <v>30036</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr">
@@ -24215,18 +24215,18 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>23686890</v>
+        <v>22561600</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>30446</v>
+        <v>28999</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -24525,18 +24525,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>16886535</v>
+        <v>16168800</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>31271</v>
+        <v>29942</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -24587,18 +24587,18 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>23612585</v>
+        <v>22490900</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>30350</v>
+        <v>28909</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -24897,18 +24897,18 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>16833460</v>
+        <v>16117900</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>31173</v>
+        <v>29848</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -24959,18 +24959,18 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>23539245</v>
+        <v>22421000</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>30256</v>
+        <v>28819</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25269,18 +25269,18 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>16780385</v>
+        <v>16067100</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>31075</v>
+        <v>29754</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N389" s="3" t="inlineStr">
@@ -25331,18 +25331,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>23464940</v>
+        <v>22350300</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>30161</v>
+        <v>28728</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -25641,18 +25641,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>16675200</v>
+        <v>15966500</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>30880</v>
+        <v>29568</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -25703,18 +25703,18 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>23316330</v>
+        <v>22208700</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>29970</v>
+        <v>28546</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N396" s="3" t="inlineStr">
@@ -26013,18 +26013,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>16516940</v>
+        <v>15814900</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>30587</v>
+        <v>29287</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -26075,18 +26075,18 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>8.08%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>23095345</v>
+        <v>21998200</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>29686</v>
+        <v>28275</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -676,7 +676,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2369,18 +2369,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6253800</v>
+        <v>6285300</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>27309</v>
+        <v>27447</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -13845,18 +13845,18 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>6175100</v>
+        <v>6206200</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>26966</v>
+        <v>27101</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13969,18 +13969,18 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>11012900</v>
+        <v>11068300</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>30935</v>
+        <v>31091</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14031,18 +14031,18 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>11962700</v>
+        <v>12022900</v>
       </c>
       <c r="L208" s="5" t="n">
-        <v>32596</v>
+        <v>32760</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%) + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14481,18 +14481,18 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>17888300</v>
+        <v>17981800</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>33126</v>
+        <v>33300</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14853,18 +14853,18 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>17685900</v>
+        <v>17778300</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>32752</v>
+        <v>32923</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15225,18 +15225,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>17585200</v>
+        <v>17677000</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>32565</v>
+        <v>32735</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15969,18 +15969,18 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>17483600</v>
+        <v>17574900</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>32377</v>
+        <v>32546</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16341,18 +16341,18 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>17432800</v>
+        <v>17523800</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>32283</v>
+        <v>32451</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -18635,18 +18635,18 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>23761200</v>
+        <v>23885900</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>30541</v>
+        <v>30702</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -19379,18 +19379,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>23619700</v>
+        <v>23743700</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>30360</v>
+        <v>30519</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -19751,18 +19751,18 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>23548900</v>
+        <v>23672500</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>30269</v>
+        <v>30427</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -20061,18 +20061,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>16876600</v>
+        <v>16964700</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>31253</v>
+        <v>31416</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -20123,18 +20123,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>23479000</v>
+        <v>23602200</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>30179</v>
+        <v>30337</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20495,18 +20495,18 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>23408200</v>
+        <v>23531100</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>30088</v>
+        <v>30246</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -20805,18 +20805,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>16775800</v>
+        <v>16863400</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>31066</v>
+        <v>31229</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20867,18 +20867,18 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>23337400</v>
+        <v>23459900</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>29997</v>
+        <v>30154</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N318" s="3" t="inlineStr">
@@ -21549,18 +21549,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>16725000</v>
+        <v>16812300</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>30972</v>
+        <v>31134</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -21611,18 +21611,18 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>23266700</v>
+        <v>23388800</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>29906</v>
+        <v>30063</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -21921,18 +21921,18 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>16674100</v>
+        <v>16761200</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>30878</v>
+        <v>31039</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22293,18 +22293,18 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>16624300</v>
+        <v>16711100</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>30786</v>
+        <v>30946</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr">
@@ -22355,18 +22355,18 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>23126100</v>
+        <v>23247500</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>29725</v>
+        <v>29881</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22665,18 +22665,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>16573500</v>
+        <v>16660100</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>30692</v>
+        <v>30852</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -22727,18 +22727,18 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>23055200</v>
+        <v>23176200</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>29634</v>
+        <v>29789</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23037,18 +23037,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>16522700</v>
+        <v>16608900</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>30598</v>
+        <v>30757</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -23409,18 +23409,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>16269500</v>
+        <v>16354500</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>30129</v>
+        <v>30286</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23471,18 +23471,18 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>22632400</v>
+        <v>22751200</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>29090</v>
+        <v>29243</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -23781,18 +23781,18 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>16219600</v>
+        <v>16304300</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>30036</v>
+        <v>30193</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N365" s="3" t="inlineStr">
@@ -23843,18 +23843,18 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>22561600</v>
+        <v>22680100</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>28999</v>
+        <v>29152</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -24153,18 +24153,18 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>16219600</v>
+        <v>16304300</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>30036</v>
+        <v>30193</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr">
@@ -24215,18 +24215,18 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>22561600</v>
+        <v>22680100</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>28999</v>
+        <v>29152</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -24525,18 +24525,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>16168800</v>
+        <v>16253200</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>29942</v>
+        <v>30099</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -24587,18 +24587,18 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>22490900</v>
+        <v>22608900</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>28909</v>
+        <v>29060</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -24897,18 +24897,18 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>16117900</v>
+        <v>16202100</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>29848</v>
+        <v>30004</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -24959,18 +24959,18 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>22421000</v>
+        <v>22538700</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>28819</v>
+        <v>28970</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25269,18 +25269,18 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>16067100</v>
+        <v>16151000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>29754</v>
+        <v>29909</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N389" s="3" t="inlineStr">
@@ -25331,18 +25331,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>22350300</v>
+        <v>22467600</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>28728</v>
+        <v>28879</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -25641,18 +25641,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>15966500</v>
+        <v>16049800</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>29568</v>
+        <v>29722</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -25703,18 +25703,18 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>22208700</v>
+        <v>22325300</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>28546</v>
+        <v>28696</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N396" s="3" t="inlineStr">
@@ -26013,18 +26013,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>15814900</v>
+        <v>15897500</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>29287</v>
+        <v>29440</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -26075,18 +26075,18 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>8.08%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>21998200</v>
+        <v>22113700</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>28275</v>
+        <v>28424</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅 + 恒地會回贈(0.5%)</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -676,7 +676,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 特別折扣 (減5.5%)</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -676,7 +676,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2369,18 +2369,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6285300</v>
+        <v>6285370</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>27447</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
@@ -13856,7 +13856,7 @@
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -13969,18 +13969,18 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>11068300</v>
+        <v>11068330</v>
       </c>
       <c r="L207" s="5" t="n">
         <v>31091</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14031,18 +14031,18 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>12022900</v>
+        <v>12022920</v>
       </c>
       <c r="L208" s="5" t="n">
         <v>32760</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14481,18 +14481,18 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>17981800</v>
+        <v>18682400</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>33300</v>
+        <v>34597</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14853,18 +14853,18 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>17778300</v>
+        <v>18471065</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>32923</v>
+        <v>34206</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15225,18 +15225,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>17677000</v>
+        <v>18365880</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>32735</v>
+        <v>34011</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15969,18 +15969,18 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>17574900</v>
+        <v>18259730</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>32546</v>
+        <v>33814</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16341,18 +16341,18 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>17523800</v>
+        <v>18206655</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>32451</v>
+        <v>33716</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -18635,18 +18635,18 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>23885900</v>
+        <v>24946215</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>30702</v>
+        <v>32065</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -19379,18 +19379,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>23743700</v>
+        <v>24797605</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>30519</v>
+        <v>31874</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -19751,18 +19751,18 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>23672500</v>
+        <v>21008400</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>30427</v>
+        <v>27003</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N300" s="3" t="inlineStr">
@@ -20061,18 +20061,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>16964700</v>
+        <v>17625725</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>31416</v>
+        <v>32640</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -20123,18 +20123,18 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>23602200</v>
+        <v>20946080</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>30337</v>
+        <v>26923</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -20495,18 +20495,18 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>23531100</v>
+        <v>20882940</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>30246</v>
+        <v>26842</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N312" s="3" t="inlineStr">
@@ -20805,18 +20805,18 @@
       </c>
       <c r="J317" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K317" s="5" t="n">
-        <v>16863400</v>
+        <v>14887920</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>31229</v>
+        <v>27570</v>
       </c>
       <c r="M317" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N317" s="3" t="inlineStr">
@@ -20867,18 +20867,18 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>23459900</v>
+        <v>20819800</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>30154</v>
+        <v>26761</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N318" s="3" t="inlineStr">
@@ -21549,18 +21549,18 @@
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K329" s="5" t="n">
-        <v>16812300</v>
+        <v>14842820</v>
       </c>
       <c r="L329" s="5" t="n">
-        <v>31134</v>
+        <v>27487</v>
       </c>
       <c r="M329" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N329" s="3" t="inlineStr">
@@ -21611,18 +21611,18 @@
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K330" s="5" t="n">
-        <v>23388800</v>
+        <v>20756660</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>30063</v>
+        <v>26680</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N330" s="3" t="inlineStr">
@@ -21921,18 +21921,18 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>16761200</v>
+        <v>17414390</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>31039</v>
+        <v>32249</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22293,18 +22293,18 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>16711100</v>
+        <v>17362280</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>30946</v>
+        <v>32152</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr">
@@ -22355,18 +22355,18 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>23247500</v>
+        <v>24279400</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>29881</v>
+        <v>31207</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22665,18 +22665,18 @@
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>16660100</v>
+        <v>14708340</v>
       </c>
       <c r="L347" s="5" t="n">
-        <v>30852</v>
+        <v>27238</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N347" s="3" t="inlineStr">
@@ -22727,18 +22727,18 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>23176200</v>
+        <v>24205095</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>29789</v>
+        <v>31112</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23037,18 +23037,18 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>16608900</v>
+        <v>14663240</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>30757</v>
+        <v>27154</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N353" s="3" t="inlineStr">
@@ -23409,18 +23409,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>16354500</v>
+        <v>16991720</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>30286</v>
+        <v>31466</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23471,18 +23471,18 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>22751200</v>
+        <v>23761195</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>29243</v>
+        <v>30541</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -23781,18 +23781,18 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>16304300</v>
+        <v>16939610</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>30193</v>
+        <v>31370</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N365" s="3" t="inlineStr">
@@ -23843,18 +23843,18 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>22680100</v>
+        <v>23686890</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>29152</v>
+        <v>30446</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -24153,18 +24153,18 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>16304300</v>
+        <v>16939610</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>30193</v>
+        <v>31370</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr">
@@ -24215,18 +24215,18 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>22680100</v>
+        <v>23686890</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>29152</v>
+        <v>30446</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -24525,18 +24525,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>16253200</v>
+        <v>16886535</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>30099</v>
+        <v>31271</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -24587,18 +24587,18 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>22608900</v>
+        <v>23612585</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>29060</v>
+        <v>30350</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -24897,18 +24897,18 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>16202100</v>
+        <v>16833460</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>30004</v>
+        <v>31173</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -24959,18 +24959,18 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>22538700</v>
+        <v>23539245</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>28970</v>
+        <v>30256</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25269,18 +25269,18 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>16151000</v>
+        <v>16780385</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>29909</v>
+        <v>31075</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N389" s="3" t="inlineStr">
@@ -25331,18 +25331,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>22467600</v>
+        <v>23464940</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>28879</v>
+        <v>30161</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -25641,18 +25641,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>16049800</v>
+        <v>16675200</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>29722</v>
+        <v>30880</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -25703,18 +25703,18 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>22325300</v>
+        <v>23316330</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>28696</v>
+        <v>29970</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N396" s="3" t="inlineStr">
@@ -26013,18 +26013,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>7.12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>15897500</v>
+        <v>16516940</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>29440</v>
+        <v>30587</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -26075,18 +26075,18 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>22113700</v>
+        <v>23095345</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>28424</v>
+        <v>29686</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>現金付款計劃 - 90天成交</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -676,7 +676,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -2369,18 +2369,18 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>6285370</v>
+        <v>6285300</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>27447</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -13969,18 +13969,18 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
-        <v>11068330</v>
+        <v>11068300</v>
       </c>
       <c r="L207" s="5" t="n">
         <v>31091</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N207" s="3" t="inlineStr">
@@ -14031,18 +14031,18 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K208" s="5" t="n">
-        <v>12022920</v>
+        <v>12022900</v>
       </c>
       <c r="L208" s="5" t="n">
         <v>32760</v>
       </c>
       <c r="M208" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N208" s="3" t="inlineStr">
@@ -14481,18 +14481,18 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>18682400</v>
+        <v>17981800</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>34597</v>
+        <v>33300</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -14853,18 +14853,18 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K221" s="5" t="n">
-        <v>18471065</v>
+        <v>17778300</v>
       </c>
       <c r="L221" s="5" t="n">
-        <v>34206</v>
+        <v>32923</v>
       </c>
       <c r="M221" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N221" s="3" t="inlineStr">
@@ -15225,18 +15225,18 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>18365880</v>
+        <v>17677000</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>34011</v>
+        <v>32735</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -15969,18 +15969,18 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>18259730</v>
+        <v>17574900</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>33814</v>
+        <v>32546</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -16341,18 +16341,18 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K245" s="5" t="n">
-        <v>18206655</v>
+        <v>17523800</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>33716</v>
+        <v>32451</v>
       </c>
       <c r="M245" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N245" s="3" t="inlineStr">
@@ -18635,18 +18635,18 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>24946215</v>
+        <v>23885900</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>32065</v>
+        <v>30702</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -19379,18 +19379,18 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K294" s="5" t="n">
-        <v>24797605</v>
+        <v>23743700</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>31874</v>
+        <v>30519</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N294" s="3" t="inlineStr">
@@ -20061,18 +20061,18 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K305" s="5" t="n">
-        <v>17625725</v>
+        <v>16964700</v>
       </c>
       <c r="L305" s="5" t="n">
-        <v>32640</v>
+        <v>31416</v>
       </c>
       <c r="M305" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N305" s="3" t="inlineStr">
@@ -21921,18 +21921,18 @@
       </c>
       <c r="J335" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K335" s="5" t="n">
-        <v>17414390</v>
+        <v>16761200</v>
       </c>
       <c r="L335" s="5" t="n">
-        <v>32249</v>
+        <v>31039</v>
       </c>
       <c r="M335" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N335" s="3" t="inlineStr">
@@ -22293,18 +22293,18 @@
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K341" s="5" t="n">
-        <v>17362280</v>
+        <v>16711100</v>
       </c>
       <c r="L341" s="5" t="n">
-        <v>32152</v>
+        <v>30946</v>
       </c>
       <c r="M341" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N341" s="3" t="inlineStr">
@@ -22355,18 +22355,18 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>24279400</v>
+        <v>23247500</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>31207</v>
+        <v>29881</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -22727,18 +22727,18 @@
       </c>
       <c r="J348" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>24205095</v>
+        <v>23176200</v>
       </c>
       <c r="L348" s="5" t="n">
-        <v>31112</v>
+        <v>29789</v>
       </c>
       <c r="M348" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N348" s="3" t="inlineStr">
@@ -23409,18 +23409,18 @@
       </c>
       <c r="J359" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K359" s="5" t="n">
-        <v>16991720</v>
+        <v>16354500</v>
       </c>
       <c r="L359" s="5" t="n">
-        <v>31466</v>
+        <v>30286</v>
       </c>
       <c r="M359" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N359" s="3" t="inlineStr">
@@ -23471,18 +23471,18 @@
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K360" s="5" t="n">
-        <v>23761195</v>
+        <v>22751200</v>
       </c>
       <c r="L360" s="5" t="n">
-        <v>30541</v>
+        <v>29243</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N360" s="3" t="inlineStr">
@@ -23781,18 +23781,18 @@
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>16939610</v>
+        <v>16304300</v>
       </c>
       <c r="L365" s="5" t="n">
-        <v>31370</v>
+        <v>30193</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N365" s="3" t="inlineStr">
@@ -23843,18 +23843,18 @@
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K366" s="5" t="n">
-        <v>23686890</v>
+        <v>22680100</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>30446</v>
+        <v>29152</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N366" s="3" t="inlineStr">
@@ -24153,18 +24153,18 @@
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K371" s="5" t="n">
-        <v>16939610</v>
+        <v>16304300</v>
       </c>
       <c r="L371" s="5" t="n">
-        <v>31370</v>
+        <v>30193</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N371" s="3" t="inlineStr">
@@ -24215,18 +24215,18 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>23686890</v>
+        <v>22680100</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>30446</v>
+        <v>29152</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N372" s="3" t="inlineStr">
@@ -24525,18 +24525,18 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>16886535</v>
+        <v>16253200</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>31271</v>
+        <v>30099</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N377" s="3" t="inlineStr">
@@ -24587,18 +24587,18 @@
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K378" s="5" t="n">
-        <v>23612585</v>
+        <v>22608900</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>30350</v>
+        <v>29060</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N378" s="3" t="inlineStr">
@@ -24897,18 +24897,18 @@
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K383" s="5" t="n">
-        <v>16833460</v>
+        <v>16202100</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>31173</v>
+        <v>30004</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N383" s="3" t="inlineStr">
@@ -24959,18 +24959,18 @@
       </c>
       <c r="J384" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K384" s="5" t="n">
-        <v>23539245</v>
+        <v>22538700</v>
       </c>
       <c r="L384" s="5" t="n">
-        <v>30256</v>
+        <v>28970</v>
       </c>
       <c r="M384" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N384" s="3" t="inlineStr">
@@ -25269,18 +25269,18 @@
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>16780385</v>
+        <v>16151000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>31075</v>
+        <v>29909</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N389" s="3" t="inlineStr">
@@ -25331,18 +25331,18 @@
       </c>
       <c r="J390" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K390" s="5" t="n">
-        <v>23464940</v>
+        <v>22467600</v>
       </c>
       <c r="L390" s="5" t="n">
-        <v>30161</v>
+        <v>28879</v>
       </c>
       <c r="M390" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N390" s="3" t="inlineStr">
@@ -25641,18 +25641,18 @@
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K395" s="5" t="n">
-        <v>16675200</v>
+        <v>16049800</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>30880</v>
+        <v>29722</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N395" s="3" t="inlineStr">
@@ -25703,18 +25703,18 @@
       </c>
       <c r="J396" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K396" s="5" t="n">
-        <v>23316330</v>
+        <v>22325300</v>
       </c>
       <c r="L396" s="5" t="n">
-        <v>29970</v>
+        <v>28696</v>
       </c>
       <c r="M396" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N396" s="3" t="inlineStr">
@@ -26013,18 +26013,18 @@
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K401" s="5" t="n">
-        <v>16516940</v>
+        <v>15897500</v>
       </c>
       <c r="L401" s="5" t="n">
-        <v>30587</v>
+        <v>29440</v>
       </c>
       <c r="M401" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N401" s="3" t="inlineStr">
@@ -26075,18 +26075,18 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>7.60%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>23095345</v>
+        <v>22113700</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>29686</v>
+        <v>28424</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
         </is>
       </c>
       <c r="N402" s="3" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -26521,7 +26521,7 @@
           <t>E | 238呎 (开放式)
 $567万
 $23,804/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>F | 229呎 (开放式)
 $545万
 $23,782/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26560,7 @@
           <t>C | 367呎 (1房)
 $908万
 $24,748/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>D | 356呎 (1房)
 $783万
 $21,995/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>E | 238呎 (开放式)
 $563万
 $23,672/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>F | 229呎 (开放式)
 $670万
 $29,242/呎
-(22年-08月-25日)</t>
+(22年-08月)</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
           <t>C | 367呎 (1房)
 $898万
 $24,467/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26623,7 +26623,7 @@
           <t>D | 356呎 (1房)
 $774万
 $21,747/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -26631,7 +26631,7 @@
           <t>E | 238呎 (开放式)
 $524万
 $22,000/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -26639,7 +26639,7 @@
           <t>F | 229呎 (开放式)
 $683万
 $29,819/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
           <t>C | 367呎 (1房)
 $832万
 $22,674/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26678,7 +26678,7 @@
           <t>D | 356呎 (1房)
 $983万
 $27,619/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -26686,7 +26686,7 @@
           <t>E | 238呎 (开放式)
 $527万
 $22,125/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -26694,7 +26694,7 @@
           <t>F | 229呎 (开放式)
 $515万
 $22,501/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -26725,7 +26725,7 @@
           <t>C | 367呎 (1房)
 $830万
 $22,609/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26733,7 +26733,7 @@
           <t>D | 356呎 (1房)
 $848万
 $23,831/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -26741,7 +26741,7 @@
           <t>E | 238呎 (开放式)
 $683万
 $28,708/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -26780,7 +26780,7 @@
           <t>C | 367呎 (1房)
 $905万
 $24,670/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26788,7 +26788,7 @@
           <t>D | 356呎 (1房)
 $846万
 $23,763/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26796,7 +26796,7 @@
           <t>E | 238呎 (开放式)
 $518万
 $21,753/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -26804,7 +26804,7 @@
           <t>F | 229呎 (开放式)
 $512万
 $22,368/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -26819,7 +26819,7 @@
           <t>A | 775呎 (3房)
 $2592万
 $33,443/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -26835,7 +26835,7 @@
           <t>C | 367呎 (1房)
 $903万
 $24,601/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26843,7 +26843,7 @@
           <t>D | 356呎 (1房)
 $844万
 $23,695/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26851,7 +26851,7 @@
           <t>E | 238呎 (开放式)
 $522万
 $21,939/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -26859,7 +26859,7 @@
           <t>F | 229呎 (开放式)
 $511万
 $22,303/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -26890,7 +26890,7 @@
           <t>C | 367呎 (1房)
 $883万
 $24,048/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26898,7 +26898,7 @@
           <t>D | 356呎 (1房)
 $825万
 $23,162/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -26906,7 +26906,7 @@
           <t>E | 238呎 (开放式)
 $678万
 $28,468/呎
-(22年-05月-26日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -26914,7 +26914,7 @@
           <t>F | 229呎 (开放式)
 $650万
 $28,404/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
           <t>C | 367呎 (1房)
 $880万
 $23,977/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -26953,7 +26953,7 @@
           <t>D | 356呎 (1房)
 $822万
 $23,094/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -26961,7 +26961,7 @@
           <t>E | 238呎 (开放式)
 $513万
 $21,570/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -26969,7 +26969,7 @@
           <t>F | 229呎 (开放式)
 $508万
 $22,173/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
           <t>C | 367呎 (1房)
 $818万
 $22,283/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -27008,7 +27008,7 @@
           <t>D | 356呎 (1房)
 $820万
 $23,029/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -27016,7 +27016,7 @@
           <t>E | 238呎 (开放式)
 $674万
 $28,320/呎
-(22年-04月-24日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -27024,7 +27024,7 @@
           <t>F | 229呎 (开放式)
 $667万
 $29,126/呎
-(21年-11月-14日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
           <t>A | 775呎 (3房)
 $2522万
 $32,542/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27055,7 +27055,7 @@
           <t>C | 367呎 (1房)
 $815万
 $22,216/呎
-(25年-07月-15日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -27063,7 +27063,7 @@
           <t>D | 356呎 (1房)
 $834万
 $23,418/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -27071,7 +27071,7 @@
           <t>E | 238呎 (开放式)
 $686万
 $28,827/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -27079,7 +27079,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,152/呎
-(22年-01月-30日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
           <t>C | 367呎 (1房)
 $813万
 $22,151/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -27118,7 +27118,7 @@
           <t>D | 356呎 (1房)
 $831万
 $23,350/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -27126,7 +27126,7 @@
           <t>E | 238呎 (开放式)
 $684万
 $28,745/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -27134,7 +27134,7 @@
           <t>F | 229呎 (开放式)
 $650万
 $28,364/呎
-(22年-01月-11日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -27165,7 +27165,7 @@
           <t>C | 367呎 (1房)
 $808万
 $22,020/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -27173,7 +27173,7 @@
           <t>D | 356呎 (1房)
 $826万
 $23,212/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -27181,7 +27181,7 @@
           <t>E | 238呎 (开放式)
 $659万
 $27,705/呎
-(22年-01月-25日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -27189,7 +27189,7 @@
           <t>F | 229呎 (开放式)
 $659万
 $28,783/呎
-(21年-11月-01日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27220,7 @@
           <t>C | 367呎 (1房)
 $838万
 $22,832/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -27228,7 +27228,7 @@
           <t>D | 356呎 (1房)
 $824万
 $23,144/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -27236,7 +27236,7 @@
           <t>E | 238呎 (开放式)
 $664万
 $27,916/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -27244,7 +27244,7 @@
           <t>F | 229呎 (开放式)
 $657万
 $28,694/呎
-(21年-11月-01日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -27275,7 +27275,7 @@
           <t>C | 367呎 (1房)
 $803万
 $21,889/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -27283,7 +27283,7 @@
           <t>D | 356呎 (1房)
 $979万
 $27,509/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -27291,7 +27291,7 @@
           <t>E | 238呎 (开放式)
 $676万
 $28,416/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -27299,7 +27299,7 @@
           <t>F | 229呎 (开放式)
 $642万
 $28,024/呎
-(21年-11月-08日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
           <t>A | 775呎 (3房)
 $2483万
 $32,041/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27330,7 +27330,7 @@
           <t>C | 367呎 (1房)
 $1077万
 $29,343/呎
-(22年-10月-25日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -27338,7 +27338,7 @@
           <t>D | 356呎 (1房)
 $956万
 $26,866/呎
-(22年-02月-15日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -27346,7 +27346,7 @@
           <t>E | 238呎 (开放式)
 $674万
 $28,333/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -27354,7 +27354,7 @@
           <t>F | 229呎 (开放式)
 $653万
 $28,523/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27385,7 +27385,7 @@
           <t>C | 367呎 (1房)
 $1041万
 $28,378/呎
-(23年-02月-02日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -27393,7 +27393,7 @@
           <t>D | 356呎 (1房)
 $944万
 $26,506/呎
-(22年-02月-14日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -27401,7 +27401,7 @@
           <t>E | 238呎 (开放式)
 $672万
 $28,251/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -27409,7 +27409,7 @@
           <t>F | 229呎 (开放式)
 $631万
 $27,566/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27440,7 @@
           <t>C | 367呎 (1房)
 $1060万
 $28,877/呎
-(23年-05月-09日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -27448,7 +27448,7 @@
           <t>D | 356呎 (1房)
 $951万
 $26,704/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -27456,7 +27456,7 @@
           <t>E | 238呎 (开放式)
 $650万
 $27,306/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>F | 229呎 (开放式)
 $649万
 $28,352/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27495,7 +27495,7 @@
           <t>C | 367呎 (1房)
 $794万
 $21,627/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -27503,7 +27503,7 @@
           <t>D | 356呎 (1房)
 $958万
 $26,904/呎
-(22年-01月-20日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>E | 238呎 (开放式)
 $668万
 $28,086/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>F | 229呎 (开放式)
 $654万
 $28,550/呎
-(21年-09月-19日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -27550,7 +27550,7 @@
           <t>C | 367呎 (1房)
 $1011万
 $27,542/呎
-(23年-01月-16日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -27558,7 +27558,7 @@
           <t>D | 356呎 (1房)
 $965万
 $27,099/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -27566,7 +27566,7 @@
           <t>E | 238呎 (开放式)
 $646万
 $27,147/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -27574,7 +27574,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,176/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27605,7 +27605,7 @@
           <t>C | 367呎 (1房)
 $1021万
 $27,832/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27613,7 +27613,7 @@
           <t>D | 356呎 (1房)
 $965万
 $27,099/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27621,7 +27621,7 @@
           <t>E | 238呎 (开放式)
 $660万
 $27,718/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -27629,7 +27629,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,176/呎
-(21年-10月-18日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
           <t>C | 367呎 (1房)
 $1040万
 $28,326/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -27668,7 +27668,7 @@
           <t>D | 356呎 (1房)
 $962万
 $27,016/呎
-(21年-10月-24日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -27676,7 +27676,7 @@
           <t>E | 238呎 (开放式)
 $644万
 $27,067/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -27684,7 +27684,7 @@
           <t>F | 229呎 (开放式)
 $624万
 $27,231/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
           <t>C | 367呎 (1房)
 $1047万
 $28,529/呎
-(22年-10月-17日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -27723,7 +27723,7 @@
           <t>D | 356呎 (1房)
 $949万
 $26,658/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -27731,7 +27731,7 @@
           <t>E | 238呎 (开放式)
 $663万
 $27,839/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -27739,7 +27739,7 @@
           <t>F | 229呎 (开放式)
 $641万
 $28,005/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27770,7 +27770,7 @@
           <t>C | 367呎 (1房)
 $1012万
 $27,581/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -27778,7 +27778,7 @@
           <t>D | 356呎 (1房)
 $956万
 $26,851/呎
-(22年-01月-26日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -27786,7 +27786,7 @@
           <t>E | 238呎 (开放式)
 $661万
 $27,757/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -27794,7 +27794,7 @@
           <t>F | 229呎 (开放式)
 $639万
 $27,919/呎
-(21年-10月-19日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27825,7 +27825,7 @@
           <t>C | 367呎 (1房)
 $999万
 $27,208/呎
-(22年-04月-13日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -27833,7 +27833,7 @@
           <t>D | 356呎 (1房)
 $943万
 $26,498/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -27841,7 +27841,7 @@
           <t>E | 238呎 (开放式)
 $665万
 $27,957/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -27849,7 +27849,7 @@
           <t>F | 229呎 (开放式)
 $644万
 $28,113/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27880,7 +27880,7 @@
           <t>C | 367呎 (1房)
 $1004万
 $27,356/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -27888,7 +27888,7 @@
           <t>D | 356呎 (1房)
 $918万
 $25,791/呎
-(21年-10月-03日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -27896,7 +27896,7 @@
           <t>E | 238呎 (开放式)
 $641万
 $26,948/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -27904,7 +27904,7 @@
           <t>F | 229呎 (开放式)
 $635万
 $27,748/呎
-(21年-10月-31日)</t>
+(21年-10月)</t>
         </is>
       </c>
     </row>
@@ -27935,7 +27935,7 @@
           <t>C | 367呎 (1房)
 $980万
 $26,709/呎
-(21年-10月-04日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -27943,7 +27943,7 @@
           <t>D | 356呎 (1房)
 $915万
 $25,711/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -27951,7 +27951,7 @@
           <t>E | 238呎 (开放式)
 $633万
 $26,588/呎
-(21年-09月-23日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -27959,7 +27959,7 @@
           <t>F | 229呎 (开放式)
 $612万
 $26,728/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -27990,7 +27990,7 @@
           <t>C | 367呎 (1房)
 $991万
 $26,990/呎
-(21年-09月-29日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27998,7 +27998,7 @@
           <t>D | 356呎 (1房)
 $915万
 $25,711/呎
-(22年-01月-16日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -28006,7 +28006,7 @@
           <t>E | 238呎 (开放式)
 $639万
 $26,868/呎
-(22年-05月-22日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -28014,7 +28014,7 @@
           <t>F | 229呎 (开放式)
 $631万
 $27,572/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -28045,7 +28045,7 @@
           <t>C | 367呎 (1房)
 $998万
 $27,186/呎
-(21年-10月-05日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>D | 356呎 (1房)
 $922万
 $25,901/呎
-(22年-01月-23日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -28061,7 +28061,7 @@
           <t>E | 238呎 (开放式)
 $631万
 $26,508/呎
-(22年-05月-22日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -28069,7 +28069,7 @@
           <t>F | 229呎 (开放式)
 $629万
 $27,487/呎
-(22年-01月-13日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
           <t>C | 367呎 (1房)
 $984万
 $26,822/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -28108,7 +28108,7 @@
           <t>D | 356呎 (1房)
 $767万
 $21,545/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -28116,7 +28116,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,268/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -28124,7 +28124,7 @@
           <t>F | 229呎 (开放式)
 $611万
 $26,670/呎
-(22年-03月-31日)</t>
+(22年-03月)</t>
         </is>
       </c>
     </row>
@@ -28155,7 +28155,7 @@
           <t>C | 367呎 (1房)
 $991万
 $27,014/呎
-(21年-10月-07日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -28163,7 +28163,7 @@
           <t>D | 356呎 (1房)
 $760万
 $21,342/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -28171,7 +28171,7 @@
           <t>E | 238呎 (开放式)
 $633万
 $26,577/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -28179,7 +28179,7 @@
           <t>F | 229呎 (开放式)
 $599万
 $26,139/呎
-(21年-11月-15日)</t>
+(21年-11月)</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28210,7 @@
           <t>C | 367呎 (1房)
 $965万
 $26,292/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -28218,7 +28218,7 @@
           <t>D | 356呎 (1房)
 $757万
 $21,276/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28226,7 +28226,7 @@
           <t>E | 238呎 (开放式)
 $569万
 $23,900/呎
-(24年-07月-18日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -28234,7 +28234,7 @@
           <t>F | 229呎 (开放式)
 $597万
 $26,056/呎
-(21年-12月-14日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -28265,7 +28265,7 @@
           <t>C | 367呎 (1房)
 $969万
 $26,401/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28273,7 +28273,7 @@
           <t>D | 356呎 (1房)
 $753万
 $21,140/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28281,7 +28281,7 @@
           <t>E | 238呎 (开放式)
 $466万
 $19,595/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -28289,7 +28289,7 @@
           <t>F | 229呎 (开放式)
 $599万
 $26,163/呎
-(22年-02月-09日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28306,7 @@
           <t>C | 374呎 (1房)
 $971万
 $25,957/呎
-(22年-08月-28日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -28314,7 +28314,7 @@
           <t>D | 356呎 (1房)
 $745万
 $20,937/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -28322,7 +28322,7 @@
           <t>E | 238呎 (开放式)
 $462万
 $19,415/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -28330,7 +28330,7 @@
           <t>F | 229呎 (开放式)
 $587万
 $25,654/呎
-(22年-03月-06日)</t>
+(22年-03月)</t>
         </is>
       </c>
     </row>
@@ -28512,7 +28512,7 @@
           <t>E | 238呎 (开放式)
 $561万
 $23,563/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -28535,7 +28535,7 @@
           <t>A | 777呎 (3房)
 $2572万
 $33,107/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -28551,7 +28551,7 @@
           <t>C | 367呎 (1房)
 $1073万
 $29,227/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -28559,7 +28559,7 @@
           <t>D | 356呎 (1房)
 $776万
 $21,801/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28567,7 +28567,7 @@
           <t>E | 238呎 (开放式)
 $558万
 $23,435/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -28575,7 +28575,7 @@
           <t>F | 229呎 (开放式)
 $644万
 $28,131/呎
-(22年-01月-13日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28590,7 @@
           <t>A | 778呎 (3房)
 $2543万
 $32,689/呎
-(22年-03月-06日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -28606,7 +28606,7 @@
           <t>C | 367呎 (1房)
 $1039万
 $28,306/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -28614,7 +28614,7 @@
           <t>D | 356呎 (1房)
 $990万
 $27,818/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28622,7 +28622,7 @@
           <t>E | 238呎 (开放式)
 $518万
 $21,772/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -28630,7 +28630,7 @@
           <t>F | 229呎 (开放式)
 $499万
 $21,772/呎
-(25年-07月-27日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
           <t>A | 777呎 (3房)
 $2582万
 $33,230/呎
-(23年-01月-25日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -28661,7 +28661,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,738/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -28669,7 +28669,7 @@
           <t>D | 356呎 (1房)
 $763万
 $21,428/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28677,7 +28677,7 @@
           <t>E | 238呎 (开放式)
 $515万
 $21,650/呎
-(25年-06月-23日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -28685,7 +28685,7 @@
           <t>F | 229呎 (开放式)
 $496万
 $21,642/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -28700,7 +28700,7 @@
           <t>A | 777呎 (3房)
 $2521万
 $32,450/呎
-(22年-06月-12日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -28708,7 +28708,7 @@
           <t>B | 540呎 (2房)
 $1803万
 $33,385/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -28716,7 +28716,7 @@
           <t>C | 367呎 (1房)
 $1030万
 $28,065/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -28724,7 +28724,7 @@
           <t>D | 356呎 (1房)
 $761万
 $21,366/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28732,7 +28732,7 @@
           <t>E | 238呎 (开放式)
 $514万
 $21,588/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -28740,7 +28740,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,386/呎
-(24年-08月-18日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -28755,7 +28755,7 @@
           <t>A | 778呎 (3房)
 $2541万
 $32,655/呎
-(21年-10月-11日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -28771,7 +28771,7 @@
           <t>C | 367呎 (1房)
 $1027万
 $27,985/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -28779,7 +28779,7 @@
           <t>D | 356呎 (1房)
 $979万
 $27,497/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28787,7 +28787,7 @@
           <t>E | 238呎 (开放式)
 $512万
 $21,529/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -28795,7 +28795,7 @@
           <t>F | 229呎 (开放式)
 $580万
 $25,314/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
           <t>A | 777呎 (3房)
 $2507万
 $32,263/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28826,7 +28826,7 @@
           <t>C | 367呎 (1房)
 $1024万
 $27,905/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -28834,7 +28834,7 @@
           <t>D | 356呎 (1房)
 $756万
 $21,241/呎
-(25年-07月-31日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28842,7 +28842,7 @@
           <t>E | 238呎 (开放式)
 $511万
 $21,467/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -28850,7 +28850,7 @@
           <t>F | 229呎 (开放式)
 $654万
 $28,554/呎
-(22年-08月-10日)</t>
+(22年-08月)</t>
         </is>
       </c>
     </row>
@@ -28865,7 +28865,7 @@
           <t>A | 778呎 (3房)
 $2526万
 $32,466/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -28873,7 +28873,7 @@
           <t>B | 540呎 (2房)
 $1806万
 $33,445/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28881,7 +28881,7 @@
           <t>C | 367呎 (1房)
 $1021万
 $27,827/呎
-(21年-12月-19日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -28889,7 +28889,7 @@
           <t>D | 356呎 (1房)
 $754万
 $21,177/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28897,7 +28897,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,404/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -28905,7 +28905,7 @@
           <t>F | 229呎 (开放式)
 $626万
 $27,322/呎
-(22年-06月-05日)</t>
+(22年-06月)</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28920,7 @@
           <t>A | 777呎 (3房)
 $2532万
 $32,581/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -28928,7 +28928,7 @@
           <t>B | 540呎 (2房)
 $1782万
 $33,000/呎
-(21年-10月-17日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -28936,7 +28936,7 @@
           <t>C | 367呎 (1房)
 $1029万
 $28,039/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -28944,7 +28944,7 @@
           <t>D | 356呎 (1房)
 $752万
 $21,115/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28952,7 +28952,7 @@
           <t>E | 238呎 (开放式)
 $508万
 $21,364/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -28960,7 +28960,7 @@
           <t>F | 229呎 (开放式)
 $630万
 $27,525/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
           <t>A | 777呎 (3房)
 $2485万
 $31,981/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -28983,7 +28983,7 @@
           <t>B | 540呎 (2房)
 $1814万
 $33,596/呎
-(21年-10月-10日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -28991,7 +28991,7 @@
           <t>C | 367呎 (1房)
 $1015万
 $27,666/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -28999,7 +28999,7 @@
           <t>D | 356呎 (1房)
 $750万
 $21,054/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -29007,7 +29007,7 @@
           <t>E | 238呎 (开放式)
 $660万
 $27,729/呎
-(22年-05月-17日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -29015,7 +29015,7 @@
           <t>F | 229呎 (开放式)
 $629万
 $27,446/呎
-(22年-05月-25日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -29030,7 +29030,7 @@
           <t>A | 777呎 (3房)
 $2478万
 $31,888/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29038,7 +29038,7 @@
           <t>B | 540呎 (2房)
 $1791万
 $33,163/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29046,7 +29046,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,748/呎
-(21年-12月-02日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -29054,7 +29054,7 @@
           <t>D | 356呎 (1房)
 $747万
 $20,992/呎
-(25年-06月-24日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -29062,7 +29062,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,371/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -29070,7 +29070,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,077/呎
-(22年-05月-11日)</t>
+(22年-05月)</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
           <t>A | 777呎 (3房)
 $2470万
 $31,794/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>B | 540呎 (2房)
 $1767万
 $32,725/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29101,7 +29101,7 @@
           <t>C | 367呎 (1房)
 $1020万
 $27,795/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>D | 356呎 (1房)
 $982万
 $27,578/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -29117,7 +29117,7 @@
           <t>E | 238呎 (开放式)
 $663万
 $27,860/呎
-(22年-04月-24日)</t>
+(22年-04月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -29125,7 +29125,7 @@
           <t>F | 229呎 (开放式)
 $618万
 $26,998/呎
-(21年-12月-27日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29148,7 @@
           <t>B | 540呎 (2房)
 $1757万
 $32,531/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29156,7 +29156,7 @@
           <t>C | 367呎 (1房)
 $994万
 $27,076/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,312/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -29172,7 +29172,7 @@
           <t>E | 238呎 (开放式)
 $496万
 $20,827/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -29180,7 +29180,7 @@
           <t>F | 229呎 (开放式)
 $634万
 $27,684/呎
-(21年-12月-10日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29195,7 @@
           <t>A | 777呎 (3房)
 $2449万
 $31,513/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29203,7 +29203,7 @@
           <t>B | 540呎 (2房)
 $1733万
 $32,098/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29211,7 +29211,7 @@
           <t>C | 367呎 (1房)
 $991万
 $26,996/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29219,7 +29219,7 @@
           <t>D | 356呎 (1房)
 $944万
 $26,510/呎
-(21年-09月-26日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>E | 238呎 (开放式)
 $494万
 $20,768/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -29235,7 +29235,7 @@
           <t>F | 229呎 (开放式)
 $619万
 $27,035/呎
-(22年-02月-08日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
           <t>B | 540呎 (2房)
 $1728万
 $32,003/呎
-(22年-01月-10日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29266,7 +29266,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,918/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29274,7 +29274,7 @@
           <t>D | 356呎 (1房)
 $960万
 $26,980/呎
-(21年-11月-17日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -29282,7 +29282,7 @@
           <t>E | 238呎 (开放式)
 $655万
 $27,537/呎
-(22年-05月-02日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -29290,7 +29290,7 @@
           <t>F | 229呎 (开放式)
 $617万
 $26,955/呎
-(22年-02月-08日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29313,7 @@
           <t>B | 540呎 (2房)
 $1740万
 $32,230/呎
-(22年-07月-31日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29321,7 +29321,7 @@
           <t>C | 367呎 (1房)
 $985万
 $26,838/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29329,7 +29329,7 @@
           <t>D | 356呎 (1房)
 $958万
 $26,900/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -29337,7 +29337,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,457/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -29345,7 +29345,7 @@
           <t>F | 229呎 (开放式)
 $615万
 $26,872/呎
-(22年-01月-09日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
           <t>C | 367呎 (1房)
 $982万
 $26,760/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29384,7 +29384,7 @@
           <t>D | 356呎 (1房)
 $925万
 $25,997/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -29392,7 +29392,7 @@
           <t>E | 238呎 (开放式)
 $665万
 $27,946/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -29400,7 +29400,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,071/呎
-(22年-01月-09日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29423,7 @@
           <t>B | 540呎 (2房)
 $1748万
 $32,375/呎
-(21年-10月-14日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29431,7 +29431,7 @@
           <t>C | 367呎 (1房)
 $989万
 $26,961/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -29439,7 +29439,7 @@
           <t>D | 356呎 (1房)
 $932万
 $26,192/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29447,7 +29447,7 @@
           <t>E | 238呎 (开放式)
 $656万
 $27,579/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -29455,7 +29455,7 @@
           <t>F | 229呎 (开放式)
 $612万
 $26,708/呎
-(22年-01月-06日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
           <t>C | 367呎 (1房)
 $987万
 $26,883/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -29494,7 +29494,7 @@
           <t>D | 356呎 (1房)
 $920万
 $25,839/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29502,7 +29502,7 @@
           <t>E | 238呎 (开放式)
 $654万
 $27,498/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -29510,7 +29510,7 @@
           <t>F | 229呎 (开放式)
 $610万
 $26,628/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29525,7 @@
           <t>A | 777呎 (3房)
 $2405万
 $30,949/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29533,7 +29533,7 @@
           <t>B | 540呎 (2房)
 $1720万
 $31,844/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -29541,7 +29541,7 @@
           <t>C | 367呎 (1房)
 $973万
 $26,522/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -29549,7 +29549,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29557,7 +29557,7 @@
           <t>E | 238呎 (开放式)
 $659万
 $27,699/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -29565,7 +29565,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29596,7 +29596,7 @@
           <t>C | 367呎 (1房)
 $984万
 $26,801/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -29604,7 +29604,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29612,7 +29612,7 @@
           <t>E | 238呎 (开放式)
 $639万
 $26,851/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -29620,7 +29620,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(21年-12月-18日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29635,7 +29635,7 @@
           <t>A | 777呎 (3房)
 $2398万
 $30,856/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -29651,7 +29651,7 @@
           <t>C | 367呎 (1房)
 $981万
 $26,723/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -29659,7 +29659,7 @@
           <t>D | 356呎 (1房)
 $943万
 $26,493/呎
-(21年-11月-16日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29667,7 +29667,7 @@
           <t>E | 238呎 (开放式)
 $657万
 $27,617/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -29675,7 +29675,7 @@
           <t>F | 229呎 (开放式)
 $600万
 $26,189/呎
-(21年-12月-28日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29706,7 @@
           <t>C | 367呎 (1房)
 $998万
 $27,197/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -29714,7 +29714,7 @@
           <t>D | 356呎 (1房)
 $940万
 $26,413/呎
-(21年-09月-03日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29722,7 +29722,7 @@
           <t>E | 238呎 (开放式)
 $649万
 $27,253/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -29730,7 +29730,7 @@
           <t>F | 229呎 (开放式)
 $598万
 $26,106/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
           <t>C | 367呎 (1房)
 $995万
 $27,117/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -29769,7 +29769,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,331/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29777,7 +29777,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,452/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -29785,7 +29785,7 @@
           <t>F | 229呎 (开放式)
 $609万
 $26,575/呎
-(21年-12月-29日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29800,7 +29800,7 @@
           <t>A | 777呎 (3房)
 $2376万
 $30,575/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -29816,7 +29816,7 @@
           <t>C | 367呎 (1房)
 $972万
 $26,482/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -29824,7 +29824,7 @@
           <t>D | 356呎 (1房)
 $906万
 $25,447/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29832,7 +29832,7 @@
           <t>E | 238呎 (开放式)
 $480万
 $20,162/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -29840,7 +29840,7 @@
           <t>F | 229呎 (开放式)
 $613万
 $26,764/呎
-(21年-12月-28日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29871,7 +29871,7 @@
           <t>C | 367呎 (1房)
 $957万
 $26,085/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -29879,7 +29879,7 @@
           <t>D | 356呎 (1房)
 $909万
 $25,540/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29887,7 +29887,7 @@
           <t>E | 238呎 (开放式)
 $634万
 $26,650/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -29895,7 +29895,7 @@
           <t>F | 229呎 (开放式)
 $597万
 $26,054/呎
-(21年-12月-29日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29926,7 @@
           <t>C | 367呎 (1房)
 $974万
 $26,545/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -29934,7 +29934,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,226/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -29942,7 +29942,7 @@
           <t>E | 238呎 (开放式)
 $632万
 $26,553/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -29950,7 +29950,7 @@
           <t>F | 229呎 (开放式)
 $589万
 $25,704/呎
-(22年-01月-06日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -29981,7 +29981,7 @@
           <t>C | 367呎 (1房)
 $954万
 $26,004/呎
-(21年-09月-27日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -29989,7 +29989,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,218/呎
-(21年-12月-05日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -29997,7 +29997,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,276/呎
-(21年-11月-25日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -30005,7 +30005,7 @@
           <t>F | 229呎 (开放式)
 $595万
 $25,974/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -30036,7 +30036,7 @@
           <t>C | 367呎 (1房)
 $991万
 $27,002/呎
-(21年-11月-18日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -30044,7 +30044,7 @@
           <t>D | 356呎 (1房)
 $904万
 $25,397/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -30052,7 +30052,7 @@
           <t>E | 238呎 (开放式)
 $631万
 $26,505/呎
-(22年-01月-06日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -30060,7 +30060,7 @@
           <t>F | 229呎 (开放式)
 $593万
 $25,890/呎
-(22年-01月-10日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -30091,7 +30091,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,919/呎
-(21年-11月-18日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -30099,7 +30099,7 @@
           <t>D | 356呎 (1房)
 $914万
 $25,681/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -30107,7 +30107,7 @@
           <t>E | 238呎 (开放式)
 $622万
 $26,133/呎
-(22年-03月-02日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -30115,7 +30115,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,380/呎
-(22年-01月-23日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -30146,7 +30146,7 @@
           <t>C | 367呎 (1房)
 $975万
 $26,564/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -30154,7 +30154,7 @@
           <t>D | 356呎 (1房)
 $896万
 $25,179/呎
-(21年-11月-09日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -30162,7 +30162,7 @@
           <t>E | 238呎 (开放式)
 $627万
 $26,327/呎
-(22年-02月-08日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -30170,7 +30170,7 @@
           <t>F | 229呎 (开放式)
 $582万
 $25,400/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
           <t>C | 367呎 (1房)
 $738万
 $20,096/呎
-(25年-06月-22日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -30209,7 +30209,7 @@
           <t>D | 356呎 (1房)
 $875万
 $24,583/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -30217,7 +30217,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,247/呎
-(22年-07月-24日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -30225,7 +30225,7 @@
           <t>F | 229呎 (开放式)
 $592万
 $25,848/呎
-(22年-02月-08日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -30256,7 +30256,7 @@
           <t>C | 367呎 (1房)
 $936万
 $25,510/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -30264,7 +30264,7 @@
           <t>D | 356呎 (1房)
 $870万
 $24,425/呎
-(22年-03月-27日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -30272,7 +30272,7 @@
           <t>E | 238呎 (开放式)
 $621万
 $26,085/呎
-(22年-03月-27日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -30280,7 +30280,7 @@
           <t>F | 229呎 (开放式)
 $577万
 $25,186/呎
-(22年-02月-10日)</t>
+(22年-02月)</t>
         </is>
       </c>
     </row>
@@ -30297,7 +30297,7 @@
           <t>C | 374呎 (1房)
 $739万
 $19,765/呎
-(25年-08月-12日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -30305,7 +30305,7 @@
           <t>D | 356呎 (1房)
 $861万
 $24,188/呎
-(22年-05月-02日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -30313,7 +30313,7 @@
           <t>E | 238呎 (开放式)
 $609万
 $25,574/呎
-(22年-08月-08日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -30321,7 +30321,7 @@
           <t>F | 229呎 (开放式)
 $576万
 $25,139/呎
-(22年-03月-03日)</t>
+(22年-03月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -26521,7 +26521,7 @@
           <t>E | 238呎 (开放式)
 $567万
 $23,804/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>F | 229呎 (开放式)
 $545万
 $23,782/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -26560,7 +26560,7 @@
           <t>C | 367呎 (1房)
 $908万
 $24,748/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>D | 356呎 (1房)
 $783万
 $21,995/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>E | 238呎 (开放式)
 $563万
 $23,672/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>F | 229呎 (开放式)
 $670万
 $29,242/呎
-(22年-08月)</t>
+(22年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -26615,7 +26615,7 @@
           <t>C | 367呎 (1房)
 $898万
 $24,467/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -26623,7 +26623,7 @@
           <t>D | 356呎 (1房)
 $774万
 $21,747/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -26631,7 +26631,7 @@
           <t>E | 238呎 (开放式)
 $524万
 $22,000/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -26639,7 +26639,7 @@
           <t>F | 229呎 (开放式)
 $683万
 $29,819/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -26670,7 +26670,7 @@
           <t>C | 367呎 (1房)
 $832万
 $22,674/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -26678,7 +26678,7 @@
           <t>D | 356呎 (1房)
 $983万
 $27,619/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -26686,7 +26686,7 @@
           <t>E | 238呎 (开放式)
 $527万
 $22,125/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -26694,7 +26694,7 @@
           <t>F | 229呎 (开放式)
 $515万
 $22,501/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
     </row>
@@ -26725,7 +26725,7 @@
           <t>C | 367呎 (1房)
 $830万
 $22,609/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -26733,7 +26733,7 @@
           <t>D | 356呎 (1房)
 $848万
 $23,831/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -26741,7 +26741,7 @@
           <t>E | 238呎 (开放式)
 $683万
 $28,708/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
@@ -26780,7 +26780,7 @@
           <t>C | 367呎 (1房)
 $905万
 $24,670/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26788,7 +26788,7 @@
           <t>D | 356呎 (1房)
 $846万
 $23,763/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26796,7 +26796,7 @@
           <t>E | 238呎 (开放式)
 $518万
 $21,753/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -26804,7 +26804,7 @@
           <t>F | 229呎 (开放式)
 $512万
 $22,368/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -26819,7 +26819,7 @@
           <t>A | 775呎 (3房)
 $2592万
 $33,443/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -26835,7 +26835,7 @@
           <t>C | 367呎 (1房)
 $903万
 $24,601/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26843,7 +26843,7 @@
           <t>D | 356呎 (1房)
 $844万
 $23,695/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26851,7 +26851,7 @@
           <t>E | 238呎 (开放式)
 $522万
 $21,939/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -26859,7 +26859,7 @@
           <t>F | 229呎 (开放式)
 $511万
 $22,303/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -26890,7 +26890,7 @@
           <t>C | 367呎 (1房)
 $883万
 $24,048/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26898,7 +26898,7 @@
           <t>D | 356呎 (1房)
 $825万
 $23,162/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -26906,7 +26906,7 @@
           <t>E | 238呎 (开放式)
 $678万
 $28,468/呎
-(22年-05月)</t>
+(22年-05月-26日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -26914,7 +26914,7 @@
           <t>F | 229呎 (开放式)
 $650万
 $28,404/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
           <t>C | 367呎 (1房)
 $880万
 $23,977/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -26953,7 +26953,7 @@
           <t>D | 356呎 (1房)
 $822万
 $23,094/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -26961,7 +26961,7 @@
           <t>E | 238呎 (开放式)
 $513万
 $21,570/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -26969,7 +26969,7 @@
           <t>F | 229呎 (开放式)
 $508万
 $22,173/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
           <t>C | 367呎 (1房)
 $818万
 $22,283/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -27008,7 +27008,7 @@
           <t>D | 356呎 (1房)
 $820万
 $23,029/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -27016,7 +27016,7 @@
           <t>E | 238呎 (开放式)
 $674万
 $28,320/呎
-(22年-04月)</t>
+(22年-04月-24日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -27024,7 +27024,7 @@
           <t>F | 229呎 (开放式)
 $667万
 $29,126/呎
-(21年-11月)</t>
+(21年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -27039,7 +27039,7 @@
           <t>A | 775呎 (3房)
 $2522万
 $32,542/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27055,7 +27055,7 @@
           <t>C | 367呎 (1房)
 $815万
 $22,216/呎
-(25年-07月)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -27063,7 +27063,7 @@
           <t>D | 356呎 (1房)
 $834万
 $23,418/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -27071,7 +27071,7 @@
           <t>E | 238呎 (开放式)
 $686万
 $28,827/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -27079,7 +27079,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,152/呎
-(22年-01月)</t>
+(22年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -27110,7 +27110,7 @@
           <t>C | 367呎 (1房)
 $813万
 $22,151/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -27118,7 +27118,7 @@
           <t>D | 356呎 (1房)
 $831万
 $23,350/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -27126,7 +27126,7 @@
           <t>E | 238呎 (开放式)
 $684万
 $28,745/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -27134,7 +27134,7 @@
           <t>F | 229呎 (开放式)
 $650万
 $28,364/呎
-(22年-01月)</t>
+(22年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -27165,7 +27165,7 @@
           <t>C | 367呎 (1房)
 $808万
 $22,020/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -27173,7 +27173,7 @@
           <t>D | 356呎 (1房)
 $826万
 $23,212/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -27181,7 +27181,7 @@
           <t>E | 238呎 (开放式)
 $659万
 $27,705/呎
-(22年-01月)</t>
+(22年-01月-25日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -27189,7 +27189,7 @@
           <t>F | 229呎 (开放式)
 $659万
 $28,783/呎
-(21年-11月)</t>
+(21年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -27220,7 +27220,7 @@
           <t>C | 367呎 (1房)
 $838万
 $22,832/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -27228,7 +27228,7 @@
           <t>D | 356呎 (1房)
 $824万
 $23,144/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -27236,7 +27236,7 @@
           <t>E | 238呎 (开放式)
 $664万
 $27,916/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -27244,7 +27244,7 @@
           <t>F | 229呎 (开放式)
 $657万
 $28,694/呎
-(21年-11月)</t>
+(21年-11月-01日)</t>
         </is>
       </c>
     </row>
@@ -27275,7 +27275,7 @@
           <t>C | 367呎 (1房)
 $803万
 $21,889/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -27283,7 +27283,7 @@
           <t>D | 356呎 (1房)
 $979万
 $27,509/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -27291,7 +27291,7 @@
           <t>E | 238呎 (开放式)
 $676万
 $28,416/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -27299,7 +27299,7 @@
           <t>F | 229呎 (开放式)
 $642万
 $28,024/呎
-(21年-11月)</t>
+(21年-11月-08日)</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
           <t>A | 775呎 (3房)
 $2483万
 $32,041/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27330,7 +27330,7 @@
           <t>C | 367呎 (1房)
 $1077万
 $29,343/呎
-(22年-10月)</t>
+(22年-10月-25日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -27338,7 +27338,7 @@
           <t>D | 356呎 (1房)
 $956万
 $26,866/呎
-(22年-02月)</t>
+(22年-02月-15日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -27346,7 +27346,7 @@
           <t>E | 238呎 (开放式)
 $674万
 $28,333/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -27354,7 +27354,7 @@
           <t>F | 229呎 (开放式)
 $653万
 $28,523/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -27385,7 +27385,7 @@
           <t>C | 367呎 (1房)
 $1041万
 $28,378/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -27393,7 +27393,7 @@
           <t>D | 356呎 (1房)
 $944万
 $26,506/呎
-(22年-02月)</t>
+(22年-02月-14日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -27401,7 +27401,7 @@
           <t>E | 238呎 (开放式)
 $672万
 $28,251/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -27409,7 +27409,7 @@
           <t>F | 229呎 (开放式)
 $631万
 $27,566/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -27440,7 +27440,7 @@
           <t>C | 367呎 (1房)
 $1060万
 $28,877/呎
-(23年-05月)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -27448,7 +27448,7 @@
           <t>D | 356呎 (1房)
 $951万
 $26,704/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -27456,7 +27456,7 @@
           <t>E | 238呎 (开放式)
 $650万
 $27,306/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>F | 229呎 (开放式)
 $649万
 $28,352/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -27495,7 +27495,7 @@
           <t>C | 367呎 (1房)
 $794万
 $21,627/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -27503,7 +27503,7 @@
           <t>D | 356呎 (1房)
 $958万
 $26,904/呎
-(22年-01月)</t>
+(22年-01月-20日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>E | 238呎 (开放式)
 $668万
 $28,086/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>F | 229呎 (开放式)
 $654万
 $28,550/呎
-(21年-09月)</t>
+(21年-09月-19日)</t>
         </is>
       </c>
     </row>
@@ -27550,7 +27550,7 @@
           <t>C | 367呎 (1房)
 $1011万
 $27,542/呎
-(23年-01月)</t>
+(23年-01月-16日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -27558,7 +27558,7 @@
           <t>D | 356呎 (1房)
 $965万
 $27,099/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -27566,7 +27566,7 @@
           <t>E | 238呎 (开放式)
 $646万
 $27,147/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -27574,7 +27574,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,176/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
     </row>
@@ -27605,7 +27605,7 @@
           <t>C | 367呎 (1房)
 $1021万
 $27,832/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -27613,7 +27613,7 @@
           <t>D | 356呎 (1房)
 $965万
 $27,099/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -27621,7 +27621,7 @@
           <t>E | 238呎 (开放式)
 $660万
 $27,718/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -27629,7 +27629,7 @@
           <t>F | 229呎 (开放式)
 $645万
 $28,176/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -27660,7 +27660,7 @@
           <t>C | 367呎 (1房)
 $1040万
 $28,326/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -27668,7 +27668,7 @@
           <t>D | 356呎 (1房)
 $962万
 $27,016/呎
-(21年-10月)</t>
+(21年-10月-24日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -27676,7 +27676,7 @@
           <t>E | 238呎 (开放式)
 $644万
 $27,067/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -27684,7 +27684,7 @@
           <t>F | 229呎 (开放式)
 $624万
 $27,231/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
           <t>C | 367呎 (1房)
 $1047万
 $28,529/呎
-(22年-10月)</t>
+(22年-10月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -27723,7 +27723,7 @@
           <t>D | 356呎 (1房)
 $949万
 $26,658/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -27731,7 +27731,7 @@
           <t>E | 238呎 (开放式)
 $663万
 $27,839/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -27739,7 +27739,7 @@
           <t>F | 229呎 (开放式)
 $641万
 $28,005/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -27770,7 +27770,7 @@
           <t>C | 367呎 (1房)
 $1012万
 $27,581/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -27778,7 +27778,7 @@
           <t>D | 356呎 (1房)
 $956万
 $26,851/呎
-(22年-01月)</t>
+(22年-01月-26日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -27786,7 +27786,7 @@
           <t>E | 238呎 (开放式)
 $661万
 $27,757/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -27794,7 +27794,7 @@
           <t>F | 229呎 (开放式)
 $639万
 $27,919/呎
-(21年-10月)</t>
+(21年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -27825,7 +27825,7 @@
           <t>C | 367呎 (1房)
 $999万
 $27,208/呎
-(22年-04月)</t>
+(22年-04月-13日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -27833,7 +27833,7 @@
           <t>D | 356呎 (1房)
 $943万
 $26,498/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -27841,7 +27841,7 @@
           <t>E | 238呎 (开放式)
 $665万
 $27,957/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -27849,7 +27849,7 @@
           <t>F | 229呎 (开放式)
 $644万
 $28,113/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -27880,7 +27880,7 @@
           <t>C | 367呎 (1房)
 $1004万
 $27,356/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -27888,7 +27888,7 @@
           <t>D | 356呎 (1房)
 $918万
 $25,791/呎
-(21年-10月)</t>
+(21年-10月-03日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -27896,7 +27896,7 @@
           <t>E | 238呎 (开放式)
 $641万
 $26,948/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -27904,7 +27904,7 @@
           <t>F | 229呎 (开放式)
 $635万
 $27,748/呎
-(21年-10月)</t>
+(21年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -27935,7 +27935,7 @@
           <t>C | 367呎 (1房)
 $980万
 $26,709/呎
-(21年-10月)</t>
+(21年-10月-04日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -27943,7 +27943,7 @@
           <t>D | 356呎 (1房)
 $915万
 $25,711/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -27951,7 +27951,7 @@
           <t>E | 238呎 (开放式)
 $633万
 $26,588/呎
-(21年-09月)</t>
+(21年-09月-23日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -27959,7 +27959,7 @@
           <t>F | 229呎 (开放式)
 $612万
 $26,728/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -27990,7 +27990,7 @@
           <t>C | 367呎 (1房)
 $991万
 $26,990/呎
-(21年-09月)</t>
+(21年-09月-29日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27998,7 +27998,7 @@
           <t>D | 356呎 (1房)
 $915万
 $25,711/呎
-(22年-01月)</t>
+(22年-01月-16日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -28006,7 +28006,7 @@
           <t>E | 238呎 (开放式)
 $639万
 $26,868/呎
-(22年-05月)</t>
+(22年-05月-22日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -28014,7 +28014,7 @@
           <t>F | 229呎 (开放式)
 $631万
 $27,572/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -28045,7 +28045,7 @@
           <t>C | 367呎 (1房)
 $998万
 $27,186/呎
-(21年-10月)</t>
+(21年-10月-05日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>D | 356呎 (1房)
 $922万
 $25,901/呎
-(22年-01月)</t>
+(22年-01月-23日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -28061,7 +28061,7 @@
           <t>E | 238呎 (开放式)
 $631万
 $26,508/呎
-(22年-05月)</t>
+(22年-05月-22日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -28069,7 +28069,7 @@
           <t>F | 229呎 (开放式)
 $629万
 $27,487/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28100,7 @@
           <t>C | 367呎 (1房)
 $984万
 $26,822/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -28108,7 +28108,7 @@
           <t>D | 356呎 (1房)
 $767万
 $21,545/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -28116,7 +28116,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,268/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -28124,7 +28124,7 @@
           <t>F | 229呎 (开放式)
 $611万
 $26,670/呎
-(22年-03月)</t>
+(22年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -28155,7 +28155,7 @@
           <t>C | 367呎 (1房)
 $991万
 $27,014/呎
-(21年-10月)</t>
+(21年-10月-07日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -28163,7 +28163,7 @@
           <t>D | 356呎 (1房)
 $760万
 $21,342/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -28171,7 +28171,7 @@
           <t>E | 238呎 (开放式)
 $633万
 $26,577/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -28179,7 +28179,7 @@
           <t>F | 229呎 (开放式)
 $599万
 $26,139/呎
-(21年-11月)</t>
+(21年-11月-15日)</t>
         </is>
       </c>
     </row>
@@ -28210,7 +28210,7 @@
           <t>C | 367呎 (1房)
 $965万
 $26,292/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -28218,7 +28218,7 @@
           <t>D | 356呎 (1房)
 $757万
 $21,276/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -28226,7 +28226,7 @@
           <t>E | 238呎 (开放式)
 $569万
 $23,900/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -28234,7 +28234,7 @@
           <t>F | 229呎 (开放式)
 $597万
 $26,056/呎
-(21年-12月)</t>
+(21年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -28265,7 +28265,7 @@
           <t>C | 367呎 (1房)
 $969万
 $26,401/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -28273,7 +28273,7 @@
           <t>D | 356呎 (1房)
 $753万
 $21,140/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -28281,7 +28281,7 @@
           <t>E | 238呎 (开放式)
 $466万
 $19,595/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -28289,7 +28289,7 @@
           <t>F | 229呎 (开放式)
 $599万
 $26,163/呎
-(22年-02月)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28306,7 @@
           <t>C | 374呎 (1房)
 $971万
 $25,957/呎
-(22年-08月)</t>
+(22年-08月-28日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -28314,7 +28314,7 @@
           <t>D | 356呎 (1房)
 $745万
 $20,937/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -28322,7 +28322,7 @@
           <t>E | 238呎 (开放式)
 $462万
 $19,415/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -28330,7 +28330,7 @@
           <t>F | 229呎 (开放式)
 $587万
 $25,654/呎
-(22年-03月)</t>
+(22年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -28512,7 +28512,7 @@
           <t>E | 238呎 (开放式)
 $561万
 $23,563/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
@@ -28535,7 +28535,7 @@
           <t>A | 777呎 (3房)
 $2572万
 $33,107/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -28551,7 +28551,7 @@
           <t>C | 367呎 (1房)
 $1073万
 $29,227/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -28559,7 +28559,7 @@
           <t>D | 356呎 (1房)
 $776万
 $21,801/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28567,7 +28567,7 @@
           <t>E | 238呎 (开放式)
 $558万
 $23,435/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -28575,7 +28575,7 @@
           <t>F | 229呎 (开放式)
 $644万
 $28,131/呎
-(22年-01月)</t>
+(22年-01月-13日)</t>
         </is>
       </c>
     </row>
@@ -28590,7 +28590,7 @@
           <t>A | 778呎 (3房)
 $2543万
 $32,689/呎
-(22年-03月)</t>
+(22年-03月-06日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -28606,7 +28606,7 @@
           <t>C | 367呎 (1房)
 $1039万
 $28,306/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -28614,7 +28614,7 @@
           <t>D | 356呎 (1房)
 $990万
 $27,818/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28622,7 +28622,7 @@
           <t>E | 238呎 (开放式)
 $518万
 $21,772/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -28630,7 +28630,7 @@
           <t>F | 229呎 (开放式)
 $499万
 $21,772/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -28645,7 +28645,7 @@
           <t>A | 777呎 (3房)
 $2582万
 $33,230/呎
-(23年-01月)</t>
+(23年-01月-25日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -28661,7 +28661,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,738/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -28669,7 +28669,7 @@
           <t>D | 356呎 (1房)
 $763万
 $21,428/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28677,7 +28677,7 @@
           <t>E | 238呎 (开放式)
 $515万
 $21,650/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -28685,7 +28685,7 @@
           <t>F | 229呎 (开放式)
 $496万
 $21,642/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -28700,7 +28700,7 @@
           <t>A | 777呎 (3房)
 $2521万
 $32,450/呎
-(22年-06月)</t>
+(22年-06月-12日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -28708,7 +28708,7 @@
           <t>B | 540呎 (2房)
 $1803万
 $33,385/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -28716,7 +28716,7 @@
           <t>C | 367呎 (1房)
 $1030万
 $28,065/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -28724,7 +28724,7 @@
           <t>D | 356呎 (1房)
 $761万
 $21,366/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28732,7 +28732,7 @@
           <t>E | 238呎 (开放式)
 $514万
 $21,588/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -28740,7 +28740,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,386/呎
-(24年-08月)</t>
+(24年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -28755,7 +28755,7 @@
           <t>A | 778呎 (3房)
 $2541万
 $32,655/呎
-(21年-10月)</t>
+(21年-10月-11日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -28771,7 +28771,7 @@
           <t>C | 367呎 (1房)
 $1027万
 $27,985/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -28779,7 +28779,7 @@
           <t>D | 356呎 (1房)
 $979万
 $27,497/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28787,7 +28787,7 @@
           <t>E | 238呎 (开放式)
 $512万
 $21,529/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -28795,7 +28795,7 @@
           <t>F | 229呎 (开放式)
 $580万
 $25,314/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
           <t>A | 777呎 (3房)
 $2507万
 $32,263/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -28826,7 +28826,7 @@
           <t>C | 367呎 (1房)
 $1024万
 $27,905/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -28834,7 +28834,7 @@
           <t>D | 356呎 (1房)
 $756万
 $21,241/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28842,7 +28842,7 @@
           <t>E | 238呎 (开放式)
 $511万
 $21,467/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -28850,7 +28850,7 @@
           <t>F | 229呎 (开放式)
 $654万
 $28,554/呎
-(22年-08月)</t>
+(22年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -28865,7 +28865,7 @@
           <t>A | 778呎 (3房)
 $2526万
 $32,466/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -28873,7 +28873,7 @@
           <t>B | 540呎 (2房)
 $1806万
 $33,445/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28881,7 +28881,7 @@
           <t>C | 367呎 (1房)
 $1021万
 $27,827/呎
-(21年-12月)</t>
+(21年-12月-19日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -28889,7 +28889,7 @@
           <t>D | 356呎 (1房)
 $754万
 $21,177/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28897,7 +28897,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,404/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -28905,7 +28905,7 @@
           <t>F | 229呎 (开放式)
 $626万
 $27,322/呎
-(22年-06月)</t>
+(22年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28920,7 @@
           <t>A | 777呎 (3房)
 $2532万
 $32,581/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -28928,7 +28928,7 @@
           <t>B | 540呎 (2房)
 $1782万
 $33,000/呎
-(21年-10月)</t>
+(21年-10月-17日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -28936,7 +28936,7 @@
           <t>C | 367呎 (1房)
 $1029万
 $28,039/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -28944,7 +28944,7 @@
           <t>D | 356呎 (1房)
 $752万
 $21,115/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28952,7 +28952,7 @@
           <t>E | 238呎 (开放式)
 $508万
 $21,364/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -28960,7 +28960,7 @@
           <t>F | 229呎 (开放式)
 $630万
 $27,525/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
           <t>A | 777呎 (3房)
 $2485万
 $31,981/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -28983,7 +28983,7 @@
           <t>B | 540呎 (2房)
 $1814万
 $33,596/呎
-(21年-10月)</t>
+(21年-10月-10日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -28991,7 +28991,7 @@
           <t>C | 367呎 (1房)
 $1015万
 $27,666/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -28999,7 +28999,7 @@
           <t>D | 356呎 (1房)
 $750万
 $21,054/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -29007,7 +29007,7 @@
           <t>E | 238呎 (开放式)
 $660万
 $27,729/呎
-(22年-05月)</t>
+(22年-05月-17日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -29015,7 +29015,7 @@
           <t>F | 229呎 (开放式)
 $629万
 $27,446/呎
-(22年-05月)</t>
+(22年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -29030,7 +29030,7 @@
           <t>A | 777呎 (3房)
 $2478万
 $31,888/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -29038,7 +29038,7 @@
           <t>B | 540呎 (2房)
 $1791万
 $33,163/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -29046,7 +29046,7 @@
           <t>C | 367呎 (1房)
 $1055万
 $28,748/呎
-(21年-12月)</t>
+(21年-12月-02日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -29054,7 +29054,7 @@
           <t>D | 356呎 (1房)
 $747万
 $20,992/呎
-(25年-06月)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -29062,7 +29062,7 @@
           <t>E | 238呎 (开放式)
 $509万
 $21,371/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -29070,7 +29070,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,077/呎
-(22年-05月)</t>
+(22年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -29085,7 +29085,7 @@
           <t>A | 777呎 (3房)
 $2470万
 $31,794/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -29093,7 +29093,7 @@
           <t>B | 540呎 (2房)
 $1767万
 $32,725/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -29101,7 +29101,7 @@
           <t>C | 367呎 (1房)
 $1020万
 $27,795/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -29109,7 +29109,7 @@
           <t>D | 356呎 (1房)
 $982万
 $27,578/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -29117,7 +29117,7 @@
           <t>E | 238呎 (开放式)
 $663万
 $27,860/呎
-(22年-04月)</t>
+(22年-04月-24日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -29125,7 +29125,7 @@
           <t>F | 229呎 (开放式)
 $618万
 $26,998/呎
-(21年-12月)</t>
+(21年-12月-27日)</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29148,7 @@
           <t>B | 540呎 (2房)
 $1757万
 $32,531/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -29156,7 +29156,7 @@
           <t>C | 367呎 (1房)
 $994万
 $27,076/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,312/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -29172,7 +29172,7 @@
           <t>E | 238呎 (开放式)
 $496万
 $20,827/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -29180,7 +29180,7 @@
           <t>F | 229呎 (开放式)
 $634万
 $27,684/呎
-(21年-12月)</t>
+(21年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -29195,7 +29195,7 @@
           <t>A | 777呎 (3房)
 $2449万
 $31,513/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -29203,7 +29203,7 @@
           <t>B | 540呎 (2房)
 $1733万
 $32,098/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -29211,7 +29211,7 @@
           <t>C | 367呎 (1房)
 $991万
 $26,996/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -29219,7 +29219,7 @@
           <t>D | 356呎 (1房)
 $944万
 $26,510/呎
-(21年-09月)</t>
+(21年-09月-26日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -29227,7 +29227,7 @@
           <t>E | 238呎 (开放式)
 $494万
 $20,768/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -29235,7 +29235,7 @@
           <t>F | 229呎 (开放式)
 $619万
 $27,035/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -29258,7 +29258,7 @@
           <t>B | 540呎 (2房)
 $1728万
 $32,003/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -29266,7 +29266,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,918/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -29274,7 +29274,7 @@
           <t>D | 356呎 (1房)
 $960万
 $26,980/呎
-(21年-11月)</t>
+(21年-11月-17日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -29282,7 +29282,7 @@
           <t>E | 238呎 (开放式)
 $655万
 $27,537/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -29290,7 +29290,7 @@
           <t>F | 229呎 (开放式)
 $617万
 $26,955/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29313,7 @@
           <t>B | 540呎 (2房)
 $1740万
 $32,230/呎
-(22年-07月)</t>
+(22年-07月-31日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29321,7 +29321,7 @@
           <t>C | 367呎 (1房)
 $985万
 $26,838/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -29329,7 +29329,7 @@
           <t>D | 356呎 (1房)
 $958万
 $26,900/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -29337,7 +29337,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,457/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -29345,7 +29345,7 @@
           <t>F | 229呎 (开放式)
 $615万
 $26,872/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -29376,7 +29376,7 @@
           <t>C | 367呎 (1房)
 $982万
 $26,760/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -29384,7 +29384,7 @@
           <t>D | 356呎 (1房)
 $925万
 $25,997/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -29392,7 +29392,7 @@
           <t>E | 238呎 (开放式)
 $665万
 $27,946/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -29400,7 +29400,7 @@
           <t>F | 229呎 (开放式)
 $620万
 $27,071/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29423,7 @@
           <t>B | 540呎 (2房)
 $1748万
 $32,375/呎
-(21年-10月)</t>
+(21年-10月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29431,7 +29431,7 @@
           <t>C | 367呎 (1房)
 $989万
 $26,961/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -29439,7 +29439,7 @@
           <t>D | 356呎 (1房)
 $932万
 $26,192/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29447,7 +29447,7 @@
           <t>E | 238呎 (开放式)
 $656万
 $27,579/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -29455,7 +29455,7 @@
           <t>F | 229呎 (开放式)
 $612万
 $26,708/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
           <t>C | 367呎 (1房)
 $987万
 $26,883/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -29494,7 +29494,7 @@
           <t>D | 356呎 (1房)
 $920万
 $25,839/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29502,7 +29502,7 @@
           <t>E | 238呎 (开放式)
 $654万
 $27,498/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -29510,7 +29510,7 @@
           <t>F | 229呎 (开放式)
 $610万
 $26,628/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -29525,7 +29525,7 @@
           <t>A | 777呎 (3房)
 $2405万
 $30,949/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29533,7 +29533,7 @@
           <t>B | 540呎 (2房)
 $1720万
 $31,844/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -29541,7 +29541,7 @@
           <t>C | 367呎 (1房)
 $973万
 $26,522/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -29549,7 +29549,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29557,7 +29557,7 @@
           <t>E | 238呎 (开放式)
 $659万
 $27,699/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -29565,7 +29565,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -29596,7 +29596,7 @@
           <t>C | 367呎 (1房)
 $984万
 $26,801/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -29604,7 +29604,7 @@
           <t>D | 356呎 (1房)
 $936万
 $26,304/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29612,7 +29612,7 @@
           <t>E | 238呎 (开放式)
 $639万
 $26,851/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -29620,7 +29620,7 @@
           <t>F | 229呎 (开放式)
 $602万
 $26,268/呎
-(21年-12月)</t>
+(21年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -29635,7 +29635,7 @@
           <t>A | 777呎 (3房)
 $2398万
 $30,856/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -29651,7 +29651,7 @@
           <t>C | 367呎 (1房)
 $981万
 $26,723/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -29659,7 +29659,7 @@
           <t>D | 356呎 (1房)
 $943万
 $26,493/呎
-(21年-11月)</t>
+(21年-11月-16日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29667,7 +29667,7 @@
           <t>E | 238呎 (开放式)
 $657万
 $27,617/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -29675,7 +29675,7 @@
           <t>F | 229呎 (开放式)
 $600万
 $26,189/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -29706,7 +29706,7 @@
           <t>C | 367呎 (1房)
 $998万
 $27,197/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -29714,7 +29714,7 @@
           <t>D | 356呎 (1房)
 $940万
 $26,413/呎
-(21年-09月)</t>
+(21年-09月-03日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29722,7 +29722,7 @@
           <t>E | 238呎 (开放式)
 $649万
 $27,253/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -29730,7 +29730,7 @@
           <t>F | 229呎 (开放式)
 $598万
 $26,106/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
           <t>C | 367呎 (1房)
 $995万
 $27,117/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -29769,7 +29769,7 @@
           <t>D | 356呎 (1房)
 $937万
 $26,331/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29777,7 +29777,7 @@
           <t>E | 238呎 (开放式)
 $653万
 $27,452/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -29785,7 +29785,7 @@
           <t>F | 229呎 (开放式)
 $609万
 $26,575/呎
-(21年-12月)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -29800,7 +29800,7 @@
           <t>A | 777呎 (3房)
 $2376万
 $30,575/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -29816,7 +29816,7 @@
           <t>C | 367呎 (1房)
 $972万
 $26,482/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -29824,7 +29824,7 @@
           <t>D | 356呎 (1房)
 $906万
 $25,447/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29832,7 +29832,7 @@
           <t>E | 238呎 (开放式)
 $480万
 $20,162/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -29840,7 +29840,7 @@
           <t>F | 229呎 (开放式)
 $613万
 $26,764/呎
-(21年-12月)</t>
+(21年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -29871,7 +29871,7 @@
           <t>C | 367呎 (1房)
 $957万
 $26,085/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -29879,7 +29879,7 @@
           <t>D | 356呎 (1房)
 $909万
 $25,540/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29887,7 +29887,7 @@
           <t>E | 238呎 (开放式)
 $634万
 $26,650/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -29895,7 +29895,7 @@
           <t>F | 229呎 (开放式)
 $597万
 $26,054/呎
-(21年-12月)</t>
+(21年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -29926,7 +29926,7 @@
           <t>C | 367呎 (1房)
 $974万
 $26,545/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -29934,7 +29934,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,226/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -29942,7 +29942,7 @@
           <t>E | 238呎 (开放式)
 $632万
 $26,553/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -29950,7 +29950,7 @@
           <t>F | 229呎 (开放式)
 $589万
 $25,704/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -29981,7 +29981,7 @@
           <t>C | 367呎 (1房)
 $954万
 $26,004/呎
-(21年-09月)</t>
+(21年-09月-27日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -29989,7 +29989,7 @@
           <t>D | 356呎 (1房)
 $898万
 $25,218/呎
-(21年-12月)</t>
+(21年-12月-05日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -29997,7 +29997,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,276/呎
-(21年-11月)</t>
+(21年-11月-25日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -30005,7 +30005,7 @@
           <t>F | 229呎 (开放式)
 $595万
 $25,974/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -30036,7 +30036,7 @@
           <t>C | 367呎 (1房)
 $991万
 $27,002/呎
-(21年-11月)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -30044,7 +30044,7 @@
           <t>D | 356呎 (1房)
 $904万
 $25,397/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -30052,7 +30052,7 @@
           <t>E | 238呎 (开放式)
 $631万
 $26,505/呎
-(22年-01月)</t>
+(22年-01月-06日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -30060,7 +30060,7 @@
           <t>F | 229呎 (开放式)
 $593万
 $25,890/呎
-(22年-01月)</t>
+(22年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -30091,7 +30091,7 @@
           <t>C | 367呎 (1房)
 $988万
 $26,919/呎
-(21年-11月)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -30099,7 +30099,7 @@
           <t>D | 356呎 (1房)
 $914万
 $25,681/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -30107,7 +30107,7 @@
           <t>E | 238呎 (开放式)
 $622万
 $26,133/呎
-(22年-03月)</t>
+(22年-03月-02日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -30115,7 +30115,7 @@
           <t>F | 229呎 (开放式)
 $581万
 $25,380/呎
-(22年-01月)</t>
+(22年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -30146,7 +30146,7 @@
           <t>C | 367呎 (1房)
 $975万
 $26,564/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -30154,7 +30154,7 @@
           <t>D | 356呎 (1房)
 $896万
 $25,179/呎
-(21年-11月)</t>
+(21年-11月-09日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -30162,7 +30162,7 @@
           <t>E | 238呎 (开放式)
 $627万
 $26,327/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -30170,7 +30170,7 @@
           <t>F | 229呎 (开放式)
 $582万
 $25,400/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
           <t>C | 367呎 (1房)
 $738万
 $20,096/呎
-(25年-06月)</t>
+(25年-06月-22日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -30209,7 +30209,7 @@
           <t>D | 356呎 (1房)
 $875万
 $24,583/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -30217,7 +30217,7 @@
           <t>E | 238呎 (开放式)
 $625万
 $26,247/呎
-(22年-07月)</t>
+(22年-07月-24日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -30225,7 +30225,7 @@
           <t>F | 229呎 (开放式)
 $592万
 $25,848/呎
-(22年-02月)</t>
+(22年-02月-08日)</t>
         </is>
       </c>
     </row>
@@ -30256,7 +30256,7 @@
           <t>C | 367呎 (1房)
 $936万
 $25,510/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -30264,7 +30264,7 @@
           <t>D | 356呎 (1房)
 $870万
 $24,425/呎
-(22年-03月)</t>
+(22年-03月-27日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -30272,7 +30272,7 @@
           <t>E | 238呎 (开放式)
 $621万
 $26,085/呎
-(22年-03月)</t>
+(22年-03月-27日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -30280,7 +30280,7 @@
           <t>F | 229呎 (开放式)
 $577万
 $25,186/呎
-(22年-02月)</t>
+(22年-02月-10日)</t>
         </is>
       </c>
     </row>
@@ -30297,7 +30297,7 @@
           <t>C | 374呎 (1房)
 $739万
 $19,765/呎
-(25年-08月)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -30305,7 +30305,7 @@
           <t>D | 356呎 (1房)
 $861万
 $24,188/呎
-(22年-05月)</t>
+(22年-05月-02日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -30313,7 +30313,7 @@
           <t>E | 238呎 (开放式)
 $609万
 $25,574/呎
-(22年-08月)</t>
+(22年-08月-08日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -30321,7 +30321,7 @@
           <t>F | 229呎 (开放式)
 $576万
 $25,139/呎
-(22年-03月)</t>
+(22年-03月-03日)</t>
         </is>
       </c>
     </row>
